--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/14,09,26 Останкино КИ и ЗПФ/дв 14,09,26 млрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/14,09,26 Останкино КИ и ЗПФ/дв 14,09,26 млрсч ост ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\14,09,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5393573-96B9-4695-AE58-58208250E0A9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F7A713-6773-407E-852B-14B046A8A08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,15 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AG$119</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -697,7 +689,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -707,7 +699,6 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
@@ -717,8 +708,7 @@
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -738,7 +728,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet"/>
@@ -5839,23 +5829,24 @@
   <dimension ref="A1:AX484"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="60" style="9" customWidth="1"/>
-    <col min="2" max="2" width="3" style="9" customWidth="1"/>
-    <col min="3" max="4" width="6" style="9" customWidth="1"/>
-    <col min="5" max="6" width="7" style="9" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="3" customWidth="1"/>
+    <col min="3" max="4" width="6" customWidth="1"/>
+    <col min="5" max="6" width="7" customWidth="1"/>
     <col min="7" max="7" width="5" style="5" customWidth="1"/>
-    <col min="8" max="8" width="5" style="9" customWidth="1"/>
-    <col min="9" max="9" width="12" style="9" customWidth="1"/>
-    <col min="10" max="10" width="1" style="9" customWidth="1"/>
-    <col min="11" max="12" width="7" style="9" customWidth="1"/>
-    <col min="13" max="14" width="0.42578125" style="9" customWidth="1"/>
-    <col min="15" max="18" width="7" style="9" customWidth="1"/>
-    <col min="19" max="19" width="7" style="20" customWidth="1"/>
-    <col min="20" max="21" width="5" style="9" customWidth="1"/>
-    <col min="22" max="31" width="6" style="9" customWidth="1"/>
-    <col min="32" max="32" width="47.28515625" style="9" customWidth="1"/>
-    <col min="33" max="33" width="7" style="9" customWidth="1"/>
-    <col min="34" max="50" width="3" style="9" customWidth="1"/>
+    <col min="8" max="8" width="5" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="1" customWidth="1"/>
+    <col min="11" max="12" width="7" customWidth="1"/>
+    <col min="13" max="14" width="0.42578125" customWidth="1"/>
+    <col min="15" max="18" width="7" customWidth="1"/>
+    <col min="19" max="19" width="7" style="18" customWidth="1"/>
+    <col min="20" max="21" width="5" customWidth="1"/>
+    <col min="22" max="31" width="6" customWidth="1"/>
+    <col min="32" max="32" width="47.28515625" customWidth="1"/>
+    <col min="33" max="33" width="7" customWidth="1"/>
+    <col min="34" max="34" width="7.5703125" customWidth="1"/>
+    <col min="35" max="50" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.25">
@@ -6260,7 +6251,10 @@
         <f>SUM(AG6:AG484)</f>
         <v>7302.2100000000009</v>
       </c>
-      <c r="AH5" s="8"/>
+      <c r="AH5" s="3">
+        <f>SUM(AH6:AH484)</f>
+        <v>924.70400000000006</v>
+      </c>
       <c r="AI5" s="8"/>
       <c r="AJ5" s="8"/>
       <c r="AK5" s="8"/>
@@ -6326,7 +6320,7 @@
         <f>ROUND(Q6,0)</f>
         <v>0</v>
       </c>
-      <c r="S6" s="19"/>
+      <c r="S6" s="8"/>
       <c r="T6" s="8">
         <f>(F6+O6+R6)/P6</f>
         <v>56.890377729005429</v>
@@ -6372,7 +6366,10 @@
         <f>G6*R6</f>
         <v>0</v>
       </c>
-      <c r="AH6" s="8"/>
+      <c r="AH6" s="8">
+        <f>P6*G6</f>
+        <v>1.7314000000000001</v>
+      </c>
       <c r="AI6" s="8"/>
       <c r="AJ6" s="8"/>
       <c r="AK6" s="8"/>
@@ -6437,10 +6434,10 @@
       </c>
       <c r="Q7" s="4"/>
       <c r="R7" s="4">
-        <f t="shared" ref="R7:R70" si="5">ROUND(Q7,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S7" s="19"/>
+        <f t="shared" ref="R7:R68" si="5">ROUND(Q7,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S7" s="8"/>
       <c r="T7" s="8">
         <f t="shared" ref="T7:T70" si="6">(F7+O7+R7)/P7</f>
         <v>19.814814814814817</v>
@@ -6479,14 +6476,17 @@
       <c r="AE7" s="8">
         <v>43.2</v>
       </c>
-      <c r="AF7" s="16" t="s">
+      <c r="AF7" s="15" t="s">
         <v>40</v>
       </c>
       <c r="AG7" s="8">
         <f t="shared" ref="AG7:AG70" si="7">G7*R7</f>
         <v>0</v>
       </c>
-      <c r="AH7" s="8"/>
+      <c r="AH7" s="8">
+        <f t="shared" ref="AH7:AH70" si="8">P7*G7</f>
+        <v>6.48</v>
+      </c>
       <c r="AI7" s="8"/>
       <c r="AJ7" s="8"/>
       <c r="AK7" s="8"/>
@@ -6550,14 +6550,14 @@
         <v>4.6438000000000006</v>
       </c>
       <c r="Q8" s="4">
-        <f t="shared" ref="Q8:Q16" si="8">15*P8-O8-F8</f>
+        <f t="shared" ref="Q8:Q16" si="9">15*P8-O8-F8</f>
         <v>28.661000000000008</v>
       </c>
       <c r="R8" s="4">
         <f t="shared" si="5"/>
         <v>29</v>
       </c>
-      <c r="S8" s="19"/>
+      <c r="S8" s="8"/>
       <c r="T8" s="8">
         <f t="shared" si="6"/>
         <v>15.073000559886299</v>
@@ -6596,14 +6596,17 @@
       <c r="AE8" s="8">
         <v>5.0434000000000001</v>
       </c>
-      <c r="AF8" s="17" t="s">
+      <c r="AF8" s="16" t="s">
         <v>49</v>
       </c>
       <c r="AG8" s="8">
         <f t="shared" si="7"/>
         <v>29</v>
       </c>
-      <c r="AH8" s="8"/>
+      <c r="AH8" s="8">
+        <f t="shared" si="8"/>
+        <v>4.6438000000000006</v>
+      </c>
       <c r="AI8" s="8"/>
       <c r="AJ8" s="8"/>
       <c r="AK8" s="8"/>
@@ -6667,14 +6670,14 @@
         <v>39</v>
       </c>
       <c r="Q9" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>266</v>
       </c>
       <c r="R9" s="4">
         <f>S9</f>
         <v>450</v>
       </c>
-      <c r="S9" s="19">
+      <c r="S9" s="8">
         <f>VLOOKUP(A9,[1]Sheet!$A:$R,18,0)</f>
         <v>450</v>
       </c>
@@ -6716,14 +6719,17 @@
       <c r="AE9" s="8">
         <v>29.4</v>
       </c>
-      <c r="AF9" s="17" t="s">
+      <c r="AF9" s="16" t="s">
         <v>49</v>
       </c>
       <c r="AG9" s="8">
         <f t="shared" si="7"/>
         <v>112.5</v>
       </c>
-      <c r="AH9" s="8"/>
+      <c r="AH9" s="8">
+        <f t="shared" si="8"/>
+        <v>9.75</v>
+      </c>
       <c r="AI9" s="8"/>
       <c r="AJ9" s="8"/>
       <c r="AK9" s="8"/>
@@ -6787,14 +6793,14 @@
         <v>27.259800000000002</v>
       </c>
       <c r="Q10" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>118.29700000000005</v>
       </c>
       <c r="R10" s="4">
         <f>S10</f>
         <v>200</v>
       </c>
-      <c r="S10" s="19">
+      <c r="S10" s="8">
         <f>VLOOKUP(A10,[1]Sheet!$A:$R,18,0)</f>
         <v>200</v>
       </c>
@@ -6841,7 +6847,10 @@
         <f t="shared" si="7"/>
         <v>200</v>
       </c>
-      <c r="AH10" s="8"/>
+      <c r="AH10" s="8">
+        <f t="shared" si="8"/>
+        <v>27.259800000000002</v>
+      </c>
       <c r="AI10" s="8"/>
       <c r="AJ10" s="8"/>
       <c r="AK10" s="8"/>
@@ -6912,7 +6921,7 @@
         <f t="shared" si="5"/>
         <v>45</v>
       </c>
-      <c r="S11" s="19"/>
+      <c r="S11" s="8"/>
       <c r="T11" s="8">
         <f t="shared" si="6"/>
         <v>12.970168612191959</v>
@@ -6951,14 +6960,17 @@
       <c r="AE11" s="8">
         <v>0.1976</v>
       </c>
-      <c r="AF11" s="17" t="s">
+      <c r="AF11" s="16" t="s">
         <v>49</v>
       </c>
       <c r="AG11" s="8">
         <f t="shared" si="7"/>
         <v>45</v>
       </c>
-      <c r="AH11" s="8"/>
+      <c r="AH11" s="8">
+        <f t="shared" si="8"/>
+        <v>5.5511999999999997</v>
+      </c>
       <c r="AI11" s="8"/>
       <c r="AJ11" s="8"/>
       <c r="AK11" s="8"/>
@@ -7024,10 +7036,10 @@
         <v>62.191999999999993</v>
       </c>
       <c r="R12" s="4">
-        <f t="shared" ref="R12:R16" si="9">S12</f>
+        <f t="shared" ref="R12:R16" si="10">S12</f>
         <v>100</v>
       </c>
-      <c r="S12" s="19">
+      <c r="S12" s="8">
         <f>VLOOKUP(A12,[1]Sheet!$A:$R,18,0)</f>
         <v>100</v>
       </c>
@@ -7074,7 +7086,10 @@
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AH12" s="8"/>
+      <c r="AH12" s="8">
+        <f t="shared" si="8"/>
+        <v>7.7739999999999991</v>
+      </c>
       <c r="AI12" s="8"/>
       <c r="AJ12" s="8"/>
       <c r="AK12" s="8"/>
@@ -7140,10 +7155,10 @@
         <v>209.05680000000007</v>
       </c>
       <c r="R13" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>300</v>
       </c>
-      <c r="S13" s="19">
+      <c r="S13" s="8">
         <f>VLOOKUP(A13,[1]Sheet!$A:$R,18,0)</f>
         <v>300</v>
       </c>
@@ -7190,7 +7205,10 @@
         <f t="shared" si="7"/>
         <v>300</v>
       </c>
-      <c r="AH13" s="8"/>
+      <c r="AH13" s="8">
+        <f t="shared" si="8"/>
+        <v>27.861200000000004</v>
+      </c>
       <c r="AI13" s="8"/>
       <c r="AJ13" s="8"/>
       <c r="AK13" s="8"/>
@@ -7254,14 +7272,14 @@
         <v>32.4</v>
       </c>
       <c r="Q14" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>162</v>
       </c>
       <c r="R14" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>250</v>
       </c>
-      <c r="S14" s="19">
+      <c r="S14" s="8">
         <f>VLOOKUP(A14,[1]Sheet!$A:$R,18,0)</f>
         <v>250</v>
       </c>
@@ -7310,7 +7328,10 @@
         <f t="shared" si="7"/>
         <v>62.5</v>
       </c>
-      <c r="AH14" s="8"/>
+      <c r="AH14" s="8">
+        <f t="shared" si="8"/>
+        <v>8.1</v>
+      </c>
       <c r="AI14" s="8"/>
       <c r="AJ14" s="8"/>
       <c r="AK14" s="8"/>
@@ -7377,7 +7398,7 @@
       <c r="R15" s="4">
         <v>30</v>
       </c>
-      <c r="S15" s="19">
+      <c r="S15" s="8">
         <f>VLOOKUP(A15,[1]Sheet!$A:$R,18,0)</f>
         <v>70</v>
       </c>
@@ -7424,7 +7445,10 @@
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="AH15" s="8"/>
+      <c r="AH15" s="8">
+        <f t="shared" si="8"/>
+        <v>3.5244</v>
+      </c>
       <c r="AI15" s="8"/>
       <c r="AJ15" s="8"/>
       <c r="AK15" s="8"/>
@@ -7488,14 +7512,14 @@
         <v>39.200000000000003</v>
       </c>
       <c r="Q16" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>74</v>
       </c>
       <c r="R16" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>150</v>
       </c>
-      <c r="S16" s="19">
+      <c r="S16" s="8">
         <f>VLOOKUP(A16,[1]Sheet!$A:$R,18,0)</f>
         <v>150</v>
       </c>
@@ -7537,14 +7561,17 @@
       <c r="AE16" s="8">
         <v>37</v>
       </c>
-      <c r="AF16" s="17" t="s">
+      <c r="AF16" s="16" t="s">
         <v>49</v>
       </c>
       <c r="AG16" s="8">
         <f t="shared" si="7"/>
         <v>37.5</v>
       </c>
-      <c r="AH16" s="8"/>
+      <c r="AH16" s="8">
+        <f t="shared" si="8"/>
+        <v>9.8000000000000007</v>
+      </c>
       <c r="AI16" s="8"/>
       <c r="AJ16" s="8"/>
       <c r="AK16" s="8"/>
@@ -7615,7 +7642,7 @@
         <f t="shared" si="5"/>
         <v>157</v>
       </c>
-      <c r="S17" s="19"/>
+      <c r="S17" s="8"/>
       <c r="T17" s="8">
         <f t="shared" si="6"/>
         <v>11</v>
@@ -7659,7 +7686,10 @@
         <f t="shared" si="7"/>
         <v>62.800000000000004</v>
       </c>
-      <c r="AH17" s="8"/>
+      <c r="AH17" s="8">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
       <c r="AI17" s="8"/>
       <c r="AJ17" s="8"/>
       <c r="AK17" s="8"/>
@@ -7730,7 +7760,7 @@
         <f>S18</f>
         <v>550</v>
       </c>
-      <c r="S18" s="19">
+      <c r="S18" s="8">
         <f>VLOOKUP(A18,[1]Sheet!$A:$R,18,0)</f>
         <v>550</v>
       </c>
@@ -7777,7 +7807,10 @@
         <f t="shared" si="7"/>
         <v>550</v>
       </c>
-      <c r="AH18" s="8"/>
+      <c r="AH18" s="8">
+        <f t="shared" si="8"/>
+        <v>53.122400000000006</v>
+      </c>
       <c r="AI18" s="8"/>
       <c r="AJ18" s="8"/>
       <c r="AK18" s="8"/>
@@ -7796,94 +7829,97 @@
       <c r="AX18" s="8"/>
     </row>
     <row r="19" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="10">
         <v>-1</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="10">
         <v>5</v>
       </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="12">
-        <v>0</v>
-      </c>
-      <c r="H19" s="11">
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="11">
+        <v>0</v>
+      </c>
+      <c r="H19" s="10">
         <v>60</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11">
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11">
-        <v>0</v>
-      </c>
-      <c r="P19" s="11">
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10">
+        <v>0</v>
+      </c>
+      <c r="P19" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q19" s="13"/>
+      <c r="Q19" s="12"/>
       <c r="R19" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S19" s="19"/>
+      <c r="S19" s="8"/>
       <c r="T19" s="8" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U19" s="11" t="e">
+      <c r="U19" s="10" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V19" s="11">
-        <v>0</v>
-      </c>
-      <c r="W19" s="11">
-        <v>0</v>
-      </c>
-      <c r="X19" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="11">
+      <c r="V19" s="10">
+        <v>0</v>
+      </c>
+      <c r="W19" s="10">
+        <v>0</v>
+      </c>
+      <c r="X19" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="10">
         <v>1.6</v>
       </c>
-      <c r="Z19" s="11">
+      <c r="Z19" s="10">
         <v>0.4</v>
       </c>
-      <c r="AA19" s="11">
+      <c r="AA19" s="10">
         <v>3</v>
       </c>
-      <c r="AB19" s="11">
+      <c r="AB19" s="10">
         <v>0.4</v>
       </c>
-      <c r="AC19" s="11">
+      <c r="AC19" s="10">
         <v>2.4</v>
       </c>
-      <c r="AD19" s="11">
+      <c r="AD19" s="10">
         <v>3.2</v>
       </c>
-      <c r="AE19" s="11">
+      <c r="AE19" s="10">
         <v>2.4</v>
       </c>
-      <c r="AF19" s="11"/>
+      <c r="AF19" s="10"/>
       <c r="AG19" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH19" s="8"/>
+      <c r="AH19" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI19" s="8"/>
       <c r="AJ19" s="8"/>
       <c r="AK19" s="8"/>
@@ -7954,7 +7990,7 @@
         <f t="shared" si="5"/>
         <v>48</v>
       </c>
-      <c r="S20" s="19"/>
+      <c r="S20" s="8"/>
       <c r="T20" s="8">
         <f t="shared" si="6"/>
         <v>12.924667651403251</v>
@@ -7993,14 +8029,17 @@
       <c r="AE20" s="8">
         <v>2.3774000000000002</v>
       </c>
-      <c r="AF20" s="17" t="s">
+      <c r="AF20" s="16" t="s">
         <v>49</v>
       </c>
       <c r="AG20" s="8">
         <f t="shared" si="7"/>
         <v>48</v>
       </c>
-      <c r="AH20" s="8"/>
+      <c r="AH20" s="8">
+        <f t="shared" si="8"/>
+        <v>6.2283999999999997</v>
+      </c>
       <c r="AI20" s="8"/>
       <c r="AJ20" s="8"/>
       <c r="AK20" s="8"/>
@@ -8068,7 +8107,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S21" s="19"/>
+      <c r="S21" s="8"/>
       <c r="T21" s="8">
         <f t="shared" si="6"/>
         <v>24.123711340206189</v>
@@ -8107,14 +8146,17 @@
       <c r="AE21" s="8">
         <v>31.4</v>
       </c>
-      <c r="AF21" s="16" t="s">
+      <c r="AF21" s="15" t="s">
         <v>40</v>
       </c>
       <c r="AG21" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH21" s="8"/>
+      <c r="AH21" s="8">
+        <f t="shared" si="8"/>
+        <v>7.76</v>
+      </c>
       <c r="AI21" s="8"/>
       <c r="AJ21" s="8"/>
       <c r="AK21" s="8"/>
@@ -8178,14 +8220,14 @@
         <v>15.606399999999999</v>
       </c>
       <c r="Q22" s="4">
-        <f t="shared" ref="Q22" si="10">15*P22-O22-F22</f>
+        <f t="shared" ref="Q22" si="11">15*P22-O22-F22</f>
         <v>94.145999999999972</v>
       </c>
       <c r="R22" s="4">
         <f t="shared" si="5"/>
         <v>94</v>
       </c>
-      <c r="S22" s="19"/>
+      <c r="S22" s="8"/>
       <c r="T22" s="8">
         <f t="shared" si="6"/>
         <v>14.990644863645684</v>
@@ -8229,7 +8271,10 @@
         <f t="shared" si="7"/>
         <v>94</v>
       </c>
-      <c r="AH22" s="8"/>
+      <c r="AH22" s="8">
+        <f t="shared" si="8"/>
+        <v>15.606399999999999</v>
+      </c>
       <c r="AI22" s="8"/>
       <c r="AJ22" s="8"/>
       <c r="AK22" s="8"/>
@@ -8296,7 +8341,7 @@
       <c r="R23" s="4">
         <v>100</v>
       </c>
-      <c r="S23" s="19">
+      <c r="S23" s="8">
         <f>VLOOKUP(A23,[1]Sheet!$A:$R,18,0)</f>
         <v>150</v>
       </c>
@@ -8338,14 +8383,17 @@
       <c r="AE23" s="8">
         <v>39.200000000000003</v>
       </c>
-      <c r="AF23" s="18" t="s">
+      <c r="AF23" s="17" t="s">
         <v>43</v>
       </c>
       <c r="AG23" s="8">
         <f t="shared" si="7"/>
         <v>22</v>
       </c>
-      <c r="AH23" s="8"/>
+      <c r="AH23" s="8">
+        <f t="shared" si="8"/>
+        <v>7.2159999999999993</v>
+      </c>
       <c r="AI23" s="8"/>
       <c r="AJ23" s="8"/>
       <c r="AK23" s="8"/>
@@ -8413,7 +8461,7 @@
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="S24" s="19"/>
+      <c r="S24" s="8"/>
       <c r="T24" s="8">
         <f t="shared" si="6"/>
         <v>-17.889087656529515</v>
@@ -8452,14 +8500,17 @@
       <c r="AE24" s="8">
         <v>2.1152000000000002</v>
       </c>
-      <c r="AF24" s="17" t="s">
+      <c r="AF24" s="16" t="s">
         <v>171</v>
       </c>
       <c r="AG24" s="8">
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="AH24" s="8"/>
+      <c r="AH24" s="8">
+        <f t="shared" si="8"/>
+        <v>-0.44720000000000004</v>
+      </c>
       <c r="AI24" s="8"/>
       <c r="AJ24" s="8"/>
       <c r="AK24" s="8"/>
@@ -8478,96 +8529,99 @@
       <c r="AX24" s="8"/>
     </row>
     <row r="25" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="10">
         <v>2</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="10">
         <v>2</v>
       </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="12">
-        <v>0</v>
-      </c>
-      <c r="H25" s="11">
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="11">
+        <v>0</v>
+      </c>
+      <c r="H25" s="10">
         <v>45</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11">
+      <c r="J25" s="10"/>
+      <c r="K25" s="10">
         <v>21</v>
       </c>
-      <c r="L25" s="11">
+      <c r="L25" s="10">
         <f t="shared" si="2"/>
         <v>-21</v>
       </c>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11">
-        <v>0</v>
-      </c>
-      <c r="P25" s="11">
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10">
+        <v>0</v>
+      </c>
+      <c r="P25" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="13"/>
+      <c r="Q25" s="12"/>
       <c r="R25" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S25" s="19"/>
+      <c r="S25" s="8"/>
       <c r="T25" s="8" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U25" s="11" t="e">
+      <c r="U25" s="10" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V25" s="11">
-        <v>0</v>
-      </c>
-      <c r="W25" s="11">
-        <v>0</v>
-      </c>
-      <c r="X25" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="11">
+      <c r="V25" s="10">
+        <v>0</v>
+      </c>
+      <c r="W25" s="10">
+        <v>0</v>
+      </c>
+      <c r="X25" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="10">
         <v>-0.4</v>
       </c>
-      <c r="Z25" s="11">
+      <c r="Z25" s="10">
         <v>0.2</v>
       </c>
-      <c r="AA25" s="11">
+      <c r="AA25" s="10">
         <v>1.2</v>
       </c>
-      <c r="AB25" s="11">
+      <c r="AB25" s="10">
         <v>-1</v>
       </c>
-      <c r="AC25" s="11">
+      <c r="AC25" s="10">
         <v>0.8</v>
       </c>
-      <c r="AD25" s="11">
+      <c r="AD25" s="10">
         <v>3.4</v>
       </c>
-      <c r="AE25" s="11">
+      <c r="AE25" s="10">
         <v>0.6</v>
       </c>
-      <c r="AF25" s="11"/>
+      <c r="AF25" s="10"/>
       <c r="AG25" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH25" s="8"/>
+      <c r="AH25" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI25" s="8"/>
       <c r="AJ25" s="8"/>
       <c r="AK25" s="8"/>
@@ -8631,14 +8685,14 @@
         <v>12.222799999999999</v>
       </c>
       <c r="Q26" s="4">
-        <f t="shared" ref="Q26:Q31" si="11">15*P26-O26-F26</f>
+        <f t="shared" ref="Q26:Q31" si="12">15*P26-O26-F26</f>
         <v>91.24199999999999</v>
       </c>
       <c r="R26" s="4">
         <f t="shared" si="5"/>
         <v>91</v>
       </c>
-      <c r="S26" s="19"/>
+      <c r="S26" s="8"/>
       <c r="T26" s="8">
         <f t="shared" si="6"/>
         <v>14.980200935955756</v>
@@ -8682,7 +8736,10 @@
         <f t="shared" si="7"/>
         <v>91</v>
       </c>
-      <c r="AH26" s="8"/>
+      <c r="AH26" s="8">
+        <f t="shared" si="8"/>
+        <v>12.222799999999999</v>
+      </c>
       <c r="AI26" s="8"/>
       <c r="AJ26" s="8"/>
       <c r="AK26" s="8"/>
@@ -8746,14 +8803,14 @@
         <v>12.2</v>
       </c>
       <c r="Q27" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>103</v>
       </c>
       <c r="R27" s="4">
         <f t="shared" si="5"/>
         <v>103</v>
       </c>
-      <c r="S27" s="19"/>
+      <c r="S27" s="8"/>
       <c r="T27" s="8">
         <f t="shared" si="6"/>
         <v>15</v>
@@ -8797,7 +8854,10 @@
         <f t="shared" si="7"/>
         <v>9.27</v>
       </c>
-      <c r="AH27" s="8"/>
+      <c r="AH27" s="8">
+        <f t="shared" si="8"/>
+        <v>1.0979999999999999</v>
+      </c>
       <c r="AI27" s="8"/>
       <c r="AJ27" s="8"/>
       <c r="AK27" s="8"/>
@@ -8861,14 +8921,14 @@
         <v>10.199999999999999</v>
       </c>
       <c r="Q28" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="R28" s="4">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="S28" s="19"/>
+      <c r="S28" s="8"/>
       <c r="T28" s="8">
         <f t="shared" si="6"/>
         <v>15.000000000000002</v>
@@ -8914,7 +8974,10 @@
         <f t="shared" si="7"/>
         <v>2.16</v>
       </c>
-      <c r="AH28" s="8"/>
+      <c r="AH28" s="8">
+        <f t="shared" si="8"/>
+        <v>0.91799999999999993</v>
+      </c>
       <c r="AI28" s="8"/>
       <c r="AJ28" s="8"/>
       <c r="AK28" s="8"/>
@@ -8982,7 +9045,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S29" s="19"/>
+      <c r="S29" s="8"/>
       <c r="T29" s="8">
         <f t="shared" si="6"/>
         <v>-985</v>
@@ -9021,14 +9084,17 @@
       <c r="AE29" s="8">
         <v>13.2</v>
       </c>
-      <c r="AF29" s="16" t="s">
+      <c r="AF29" s="15" t="s">
         <v>40</v>
       </c>
       <c r="AG29" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH29" s="8"/>
+      <c r="AH29" s="8">
+        <f t="shared" si="8"/>
+        <v>-0.03</v>
+      </c>
       <c r="AI29" s="8"/>
       <c r="AJ29" s="8"/>
       <c r="AK29" s="8"/>
@@ -9092,14 +9158,14 @@
         <v>53.234999999999999</v>
       </c>
       <c r="Q30" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>14.187999999999988</v>
       </c>
       <c r="R30" s="4">
         <f>S30</f>
         <v>100</v>
       </c>
-      <c r="S30" s="19">
+      <c r="S30" s="8">
         <f>VLOOKUP(A30,[1]Sheet!$A:$R,18,0)</f>
         <v>100</v>
       </c>
@@ -9146,7 +9212,10 @@
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AH30" s="8"/>
+      <c r="AH30" s="8">
+        <f t="shared" si="8"/>
+        <v>53.234999999999999</v>
+      </c>
       <c r="AI30" s="8"/>
       <c r="AJ30" s="8"/>
       <c r="AK30" s="8"/>
@@ -9210,14 +9279,14 @@
         <v>13</v>
       </c>
       <c r="Q31" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>99</v>
       </c>
       <c r="R31" s="4">
         <f t="shared" si="5"/>
         <v>99</v>
       </c>
-      <c r="S31" s="19"/>
+      <c r="S31" s="8"/>
       <c r="T31" s="8">
         <f t="shared" si="6"/>
         <v>15</v>
@@ -9261,7 +9330,10 @@
         <f t="shared" si="7"/>
         <v>39.6</v>
       </c>
-      <c r="AH31" s="8"/>
+      <c r="AH31" s="8">
+        <f t="shared" si="8"/>
+        <v>5.2</v>
+      </c>
       <c r="AI31" s="8"/>
       <c r="AJ31" s="8"/>
       <c r="AK31" s="8"/>
@@ -9328,7 +9400,7 @@
       <c r="R32" s="4">
         <v>50</v>
       </c>
-      <c r="S32" s="19">
+      <c r="S32" s="8">
         <f>VLOOKUP(A32,[1]Sheet!$A:$R,18,0)</f>
         <v>150</v>
       </c>
@@ -9370,14 +9442,17 @@
       <c r="AE32" s="8">
         <v>56.2</v>
       </c>
-      <c r="AF32" s="16" t="s">
+      <c r="AF32" s="15" t="s">
         <v>40</v>
       </c>
       <c r="AG32" s="8">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="AH32" s="8"/>
+      <c r="AH32" s="8">
+        <f t="shared" si="8"/>
+        <v>10.48</v>
+      </c>
       <c r="AI32" s="8"/>
       <c r="AJ32" s="8"/>
       <c r="AK32" s="8"/>
@@ -9445,7 +9520,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S33" s="19"/>
+      <c r="S33" s="8"/>
       <c r="T33" s="8">
         <f t="shared" si="6"/>
         <v>20.54263565891473</v>
@@ -9484,14 +9559,17 @@
       <c r="AE33" s="8">
         <v>57</v>
       </c>
-      <c r="AF33" s="16" t="s">
+      <c r="AF33" s="15" t="s">
         <v>40</v>
       </c>
       <c r="AG33" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH33" s="8"/>
+      <c r="AH33" s="8">
+        <f t="shared" si="8"/>
+        <v>10.32</v>
+      </c>
       <c r="AI33" s="8"/>
       <c r="AJ33" s="8"/>
       <c r="AK33" s="8"/>
@@ -9510,102 +9588,105 @@
       <c r="AX33" s="8"/>
     </row>
     <row r="34" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="10">
         <v>31</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="10">
         <v>5</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="10">
         <v>14</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="10">
         <v>17</v>
       </c>
-      <c r="G34" s="12">
-        <v>0</v>
-      </c>
-      <c r="H34" s="11">
+      <c r="G34" s="11">
+        <v>0</v>
+      </c>
+      <c r="H34" s="10">
         <v>45</v>
       </c>
-      <c r="I34" s="11" t="s">
+      <c r="I34" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11">
+      <c r="J34" s="10"/>
+      <c r="K34" s="10">
         <v>15</v>
       </c>
-      <c r="L34" s="11">
+      <c r="L34" s="10">
         <f t="shared" si="2"/>
         <v>-1</v>
       </c>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="11">
-        <v>0</v>
-      </c>
-      <c r="P34" s="11">
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10">
+        <v>0</v>
+      </c>
+      <c r="P34" s="10">
         <f t="shared" si="3"/>
         <v>2.8</v>
       </c>
-      <c r="Q34" s="13"/>
+      <c r="Q34" s="12"/>
       <c r="R34" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S34" s="19"/>
+      <c r="S34" s="8"/>
       <c r="T34" s="8">
         <f t="shared" si="6"/>
         <v>6.0714285714285721</v>
       </c>
-      <c r="U34" s="11">
+      <c r="U34" s="10">
         <f t="shared" si="4"/>
         <v>6.0714285714285721</v>
       </c>
-      <c r="V34" s="11">
+      <c r="V34" s="10">
         <v>2.4</v>
       </c>
-      <c r="W34" s="11">
+      <c r="W34" s="10">
         <v>2</v>
       </c>
-      <c r="X34" s="11">
+      <c r="X34" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="Y34" s="11">
+      <c r="Y34" s="10">
         <v>1.8</v>
       </c>
-      <c r="Z34" s="11">
+      <c r="Z34" s="10">
         <v>3.4</v>
       </c>
-      <c r="AA34" s="11">
+      <c r="AA34" s="10">
         <v>0.2</v>
       </c>
-      <c r="AB34" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC34" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE34" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="10" t="s">
+      <c r="AB34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="AG34" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH34" s="8"/>
+      <c r="AH34" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI34" s="8"/>
       <c r="AJ34" s="8"/>
       <c r="AK34" s="8"/>
@@ -9624,98 +9705,101 @@
       <c r="AX34" s="8"/>
     </row>
     <row r="35" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="10">
         <v>-2</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="10">
         <v>2</v>
       </c>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="12">
-        <v>0</v>
-      </c>
-      <c r="H35" s="11">
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="11">
+        <v>0</v>
+      </c>
+      <c r="H35" s="10">
         <v>45</v>
       </c>
-      <c r="I35" s="11" t="s">
+      <c r="I35" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J35" s="11" t="s">
+      <c r="J35" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11">
+      <c r="K35" s="10"/>
+      <c r="L35" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="11">
-        <v>0</v>
-      </c>
-      <c r="P35" s="11">
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10">
+        <v>0</v>
+      </c>
+      <c r="P35" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q35" s="13"/>
+      <c r="Q35" s="12"/>
       <c r="R35" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S35" s="19"/>
+      <c r="S35" s="8"/>
       <c r="T35" s="8" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U35" s="11" t="e">
+      <c r="U35" s="10" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V35" s="11">
-        <v>0</v>
-      </c>
-      <c r="W35" s="11">
-        <v>0</v>
-      </c>
-      <c r="X35" s="11">
+      <c r="V35" s="10">
+        <v>0</v>
+      </c>
+      <c r="W35" s="10">
+        <v>0</v>
+      </c>
+      <c r="X35" s="10">
         <v>-0.2</v>
       </c>
-      <c r="Y35" s="11">
+      <c r="Y35" s="10">
         <v>-0.2</v>
       </c>
-      <c r="Z35" s="11">
+      <c r="Z35" s="10">
         <v>-0.2</v>
       </c>
-      <c r="AA35" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="11">
+      <c r="AA35" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="10">
         <v>2</v>
       </c>
-      <c r="AC35" s="11">
+      <c r="AC35" s="10">
         <v>2.8</v>
       </c>
-      <c r="AD35" s="11">
+      <c r="AD35" s="10">
         <v>3.8</v>
       </c>
-      <c r="AE35" s="11">
+      <c r="AE35" s="10">
         <v>10.6</v>
       </c>
-      <c r="AF35" s="11" t="s">
+      <c r="AF35" s="10" t="s">
         <v>76</v>
       </c>
       <c r="AG35" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH35" s="8"/>
+      <c r="AH35" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI35" s="8"/>
       <c r="AJ35" s="8"/>
       <c r="AK35" s="8"/>
@@ -9734,94 +9818,97 @@
       <c r="AX35" s="8"/>
     </row>
     <row r="36" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="10">
         <v>45.584000000000003</v>
       </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="12">
-        <v>0</v>
-      </c>
-      <c r="H36" s="11">
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="11">
+        <v>0</v>
+      </c>
+      <c r="H36" s="10">
         <v>45</v>
       </c>
-      <c r="I36" s="11" t="s">
+      <c r="I36" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11">
+      <c r="J36" s="10"/>
+      <c r="K36" s="10">
         <v>0.8</v>
       </c>
-      <c r="L36" s="11">
+      <c r="L36" s="10">
         <f t="shared" si="2"/>
         <v>-0.8</v>
       </c>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="11">
-        <v>0</v>
-      </c>
-      <c r="P36" s="11">
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="10">
+        <v>0</v>
+      </c>
+      <c r="P36" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="13"/>
+      <c r="Q36" s="12"/>
       <c r="R36" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S36" s="19"/>
+      <c r="S36" s="8"/>
       <c r="T36" s="8" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U36" s="11" t="e">
+      <c r="U36" s="10" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V36" s="11">
-        <v>0</v>
-      </c>
-      <c r="W36" s="11">
-        <v>0</v>
-      </c>
-      <c r="X36" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC36" s="11">
+      <c r="V36" s="10">
+        <v>0</v>
+      </c>
+      <c r="W36" s="10">
+        <v>0</v>
+      </c>
+      <c r="X36" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="10">
         <v>0.23780000000000001</v>
       </c>
-      <c r="AD36" s="11">
+      <c r="AD36" s="10">
         <v>1.9172</v>
       </c>
-      <c r="AE36" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="11"/>
+      <c r="AE36" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="10"/>
       <c r="AG36" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH36" s="8"/>
+      <c r="AH36" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI36" s="8"/>
       <c r="AJ36" s="8"/>
       <c r="AK36" s="8"/>
@@ -9840,98 +9927,101 @@
       <c r="AX36" s="8"/>
     </row>
     <row r="37" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="10">
         <v>30</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="10">
         <v>5</v>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="10">
         <v>-20</v>
       </c>
-      <c r="F37" s="11"/>
-      <c r="G37" s="12">
-        <v>0</v>
-      </c>
-      <c r="H37" s="11">
+      <c r="F37" s="10"/>
+      <c r="G37" s="11">
+        <v>0</v>
+      </c>
+      <c r="H37" s="10">
         <v>45</v>
       </c>
-      <c r="I37" s="11" t="s">
+      <c r="I37" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11">
+      <c r="J37" s="10"/>
+      <c r="K37" s="10">
         <v>102</v>
       </c>
-      <c r="L37" s="11">
+      <c r="L37" s="10">
         <f t="shared" si="2"/>
         <v>-122</v>
       </c>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="11">
-        <v>0</v>
-      </c>
-      <c r="P37" s="11">
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10">
+        <v>0</v>
+      </c>
+      <c r="P37" s="10">
         <f t="shared" si="3"/>
         <v>-4</v>
       </c>
-      <c r="Q37" s="13"/>
+      <c r="Q37" s="12"/>
       <c r="R37" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S37" s="19"/>
+      <c r="S37" s="8"/>
       <c r="T37" s="8">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U37" s="11">
+      <c r="U37" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V37" s="11">
+      <c r="V37" s="10">
         <v>-0.4</v>
       </c>
-      <c r="W37" s="11">
-        <v>0</v>
-      </c>
-      <c r="X37" s="11">
+      <c r="W37" s="10">
+        <v>0</v>
+      </c>
+      <c r="X37" s="10">
         <v>-1</v>
       </c>
-      <c r="Y37" s="11">
+      <c r="Y37" s="10">
         <v>-1</v>
       </c>
-      <c r="Z37" s="11">
+      <c r="Z37" s="10">
         <v>21.8</v>
       </c>
-      <c r="AA37" s="11">
+      <c r="AA37" s="10">
         <v>14.4</v>
       </c>
-      <c r="AB37" s="11">
+      <c r="AB37" s="10">
         <v>20.6</v>
       </c>
-      <c r="AC37" s="11">
+      <c r="AC37" s="10">
         <v>49.171999999999997</v>
       </c>
-      <c r="AD37" s="11">
+      <c r="AD37" s="10">
         <v>3.2</v>
       </c>
-      <c r="AE37" s="11">
+      <c r="AE37" s="10">
         <v>36.4</v>
       </c>
-      <c r="AF37" s="11"/>
+      <c r="AF37" s="10"/>
       <c r="AG37" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH37" s="8"/>
+      <c r="AH37" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI37" s="8"/>
       <c r="AJ37" s="8"/>
       <c r="AK37" s="8"/>
@@ -9980,7 +10070,7 @@
         <v>35</v>
       </c>
       <c r="L38" s="8">
-        <f t="shared" ref="L38:L69" si="12">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="13">E38-K38</f>
         <v>-1</v>
       </c>
       <c r="M38" s="8"/>
@@ -9989,7 +10079,7 @@
         <v>0</v>
       </c>
       <c r="P38" s="8">
-        <f t="shared" ref="P38:P69" si="13">E38/5</f>
+        <f t="shared" ref="P38:P69" si="14">E38/5</f>
         <v>6.8</v>
       </c>
       <c r="Q38" s="4">
@@ -10000,7 +10090,7 @@
         <f>S38</f>
         <v>100</v>
       </c>
-      <c r="S38" s="19">
+      <c r="S38" s="8">
         <f>VLOOKUP(A38,[1]Sheet!$A:$R,18,0)</f>
         <v>100</v>
       </c>
@@ -10009,7 +10099,7 @@
         <v>14.705882352941178</v>
       </c>
       <c r="U38" s="8">
-        <f t="shared" ref="U38:U69" si="14">(F38+O38)/P38</f>
+        <f t="shared" ref="U38:U69" si="15">(F38+O38)/P38</f>
         <v>0</v>
       </c>
       <c r="V38" s="8">
@@ -10047,7 +10137,10 @@
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="AH38" s="8"/>
+      <c r="AH38" s="8">
+        <f t="shared" si="8"/>
+        <v>2.04</v>
+      </c>
       <c r="AI38" s="8"/>
       <c r="AJ38" s="8"/>
       <c r="AK38" s="8"/>
@@ -10098,7 +10191,7 @@
         <v>73.3</v>
       </c>
       <c r="L39" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.0040000000000049</v>
       </c>
       <c r="M39" s="8"/>
@@ -10107,24 +10200,24 @@
         <v>104</v>
       </c>
       <c r="P39" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>15.460800000000001</v>
       </c>
       <c r="Q39" s="4">
-        <f t="shared" ref="Q39:Q43" si="15">15*P39-O39-F39</f>
+        <f t="shared" ref="Q39:Q43" si="16">15*P39-O39-F39</f>
         <v>104.91200000000001</v>
       </c>
       <c r="R39" s="4">
         <f t="shared" si="5"/>
         <v>105</v>
       </c>
-      <c r="S39" s="19"/>
+      <c r="S39" s="8"/>
       <c r="T39" s="8">
         <f t="shared" si="6"/>
         <v>15.005691814136396</v>
       </c>
       <c r="U39" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.2143226741177688</v>
       </c>
       <c r="V39" s="8">
@@ -10162,7 +10255,10 @@
         <f t="shared" si="7"/>
         <v>105</v>
       </c>
-      <c r="AH39" s="8"/>
+      <c r="AH39" s="8">
+        <f t="shared" si="8"/>
+        <v>15.460800000000001</v>
+      </c>
       <c r="AI39" s="8"/>
       <c r="AJ39" s="8"/>
       <c r="AK39" s="8"/>
@@ -10213,7 +10309,7 @@
         <v>56.3</v>
       </c>
       <c r="L40" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.4570000000000007</v>
       </c>
       <c r="M40" s="8"/>
@@ -10222,18 +10318,18 @@
         <v>111</v>
       </c>
       <c r="P40" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>11.9514</v>
       </c>
       <c r="Q40" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>26.070999999999984</v>
       </c>
       <c r="R40" s="4">
         <f>S40</f>
         <v>100</v>
       </c>
-      <c r="S40" s="19">
+      <c r="S40" s="8">
         <f>VLOOKUP(A40,[1]Sheet!$A:$R,18,0)</f>
         <v>100</v>
       </c>
@@ -10242,7 +10338,7 @@
         <v>21.185802500125508</v>
       </c>
       <c r="U40" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>12.818581923456666</v>
       </c>
       <c r="V40" s="8">
@@ -10280,7 +10376,10 @@
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AH40" s="8"/>
+      <c r="AH40" s="8">
+        <f t="shared" si="8"/>
+        <v>11.9514</v>
+      </c>
       <c r="AI40" s="8"/>
       <c r="AJ40" s="8"/>
       <c r="AK40" s="8"/>
@@ -10331,7 +10430,7 @@
         <v>84.6</v>
       </c>
       <c r="L41" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-4.2879999999999967</v>
       </c>
       <c r="M41" s="8"/>
@@ -10340,24 +10439,24 @@
         <v>102</v>
       </c>
       <c r="P41" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>16.0624</v>
       </c>
       <c r="Q41" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>75.393000000000001</v>
       </c>
       <c r="R41" s="4">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
-      <c r="S41" s="19"/>
+      <c r="S41" s="8"/>
       <c r="T41" s="8">
         <f t="shared" si="6"/>
         <v>14.975532921605739</v>
       </c>
       <c r="U41" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.306243151708339</v>
       </c>
       <c r="V41" s="8">
@@ -10395,7 +10494,10 @@
         <f t="shared" si="7"/>
         <v>75</v>
       </c>
-      <c r="AH41" s="8"/>
+      <c r="AH41" s="8">
+        <f t="shared" si="8"/>
+        <v>16.0624</v>
+      </c>
       <c r="AI41" s="8"/>
       <c r="AJ41" s="8"/>
       <c r="AK41" s="8"/>
@@ -10446,7 +10548,7 @@
         <v>80.864000000000004</v>
       </c>
       <c r="L42" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.1219999999999999</v>
       </c>
       <c r="M42" s="8"/>
@@ -10455,7 +10557,7 @@
         <v>0</v>
       </c>
       <c r="P42" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>16.397200000000002</v>
       </c>
       <c r="Q42" s="4">
@@ -10466,13 +10568,13 @@
         <f t="shared" si="5"/>
         <v>129</v>
       </c>
-      <c r="S42" s="19"/>
+      <c r="S42" s="8"/>
       <c r="T42" s="8">
         <f t="shared" si="6"/>
         <v>12.986729441611981</v>
       </c>
       <c r="U42" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.1195326031273627</v>
       </c>
       <c r="V42" s="8">
@@ -10510,7 +10612,10 @@
         <f t="shared" si="7"/>
         <v>129</v>
       </c>
-      <c r="AH42" s="8"/>
+      <c r="AH42" s="8">
+        <f t="shared" si="8"/>
+        <v>16.397200000000002</v>
+      </c>
       <c r="AI42" s="8"/>
       <c r="AJ42" s="8"/>
       <c r="AK42" s="8"/>
@@ -10561,7 +10666,7 @@
         <v>203</v>
       </c>
       <c r="L43" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-22</v>
       </c>
       <c r="M43" s="8"/>
@@ -10570,24 +10675,24 @@
         <v>0</v>
       </c>
       <c r="P43" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>36.200000000000003</v>
       </c>
       <c r="Q43" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>95</v>
       </c>
       <c r="R43" s="4">
         <f t="shared" si="5"/>
         <v>95</v>
       </c>
-      <c r="S43" s="19"/>
+      <c r="S43" s="8"/>
       <c r="T43" s="8">
         <f t="shared" si="6"/>
         <v>14.999999999999998</v>
       </c>
       <c r="U43" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>12.375690607734805</v>
       </c>
       <c r="V43" s="8">
@@ -10625,7 +10730,10 @@
         <f t="shared" si="7"/>
         <v>28.5</v>
       </c>
-      <c r="AH43" s="8"/>
+      <c r="AH43" s="8">
+        <f t="shared" si="8"/>
+        <v>10.860000000000001</v>
+      </c>
       <c r="AI43" s="8"/>
       <c r="AJ43" s="8"/>
       <c r="AK43" s="8"/>
@@ -10644,44 +10752,44 @@
       <c r="AX43" s="8"/>
     </row>
     <row r="44" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="12">
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="11">
         <v>1</v>
       </c>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11" t="s">
+      <c r="H44" s="10"/>
+      <c r="I44" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
-      <c r="O44" s="11">
-        <v>0</v>
-      </c>
-      <c r="P44" s="11">
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Q44" s="13"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="10">
+        <v>0</v>
+      </c>
+      <c r="P44" s="10">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="Q44" s="12"/>
       <c r="R44" s="4">
         <f>S44</f>
         <v>100</v>
       </c>
-      <c r="S44" s="19">
+      <c r="S44" s="8">
         <f>VLOOKUP(A44,[1]Sheet!$A:$R,18,0)</f>
         <v>100</v>
       </c>
@@ -10689,48 +10797,51 @@
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U44" s="11" t="e">
-        <f t="shared" si="14"/>
+      <c r="U44" s="10" t="e">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V44" s="11">
-        <v>0</v>
-      </c>
-      <c r="W44" s="11">
-        <v>0</v>
-      </c>
-      <c r="X44" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB44" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC44" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD44" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE44" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF44" s="11" t="s">
+      <c r="V44" s="10">
+        <v>0</v>
+      </c>
+      <c r="W44" s="10">
+        <v>0</v>
+      </c>
+      <c r="X44" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="10" t="s">
         <v>178</v>
       </c>
       <c r="AG44" s="8">
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AH44" s="8"/>
+      <c r="AH44" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI44" s="8"/>
       <c r="AJ44" s="8"/>
       <c r="AK44" s="8"/>
@@ -10781,7 +10892,7 @@
         <v>77</v>
       </c>
       <c r="L45" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5.6020000000000039</v>
       </c>
       <c r="M45" s="8"/>
@@ -10790,24 +10901,24 @@
         <v>34</v>
       </c>
       <c r="P45" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>16.520400000000002</v>
       </c>
       <c r="Q45" s="4">
-        <f t="shared" ref="Q45:Q53" si="16">15*P45-O45-F45</f>
+        <f t="shared" ref="Q45:Q53" si="17">15*P45-O45-F45</f>
         <v>128.90600000000003</v>
       </c>
       <c r="R45" s="4">
         <f t="shared" si="5"/>
         <v>129</v>
       </c>
-      <c r="S45" s="19"/>
+      <c r="S45" s="8"/>
       <c r="T45" s="8">
         <f t="shared" si="6"/>
         <v>15.005689934868403</v>
       </c>
       <c r="U45" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.1971622963124373</v>
       </c>
       <c r="V45" s="8">
@@ -10845,7 +10956,10 @@
         <f t="shared" si="7"/>
         <v>129</v>
       </c>
-      <c r="AH45" s="8"/>
+      <c r="AH45" s="8">
+        <f t="shared" si="8"/>
+        <v>16.520400000000002</v>
+      </c>
       <c r="AI45" s="8"/>
       <c r="AJ45" s="8"/>
       <c r="AK45" s="8"/>
@@ -10896,7 +11010,7 @@
         <v>411.8</v>
       </c>
       <c r="L46" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-10.800000000000011</v>
       </c>
       <c r="M46" s="8"/>
@@ -10905,18 +11019,18 @@
         <v>0</v>
       </c>
       <c r="P46" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>80.2</v>
       </c>
       <c r="Q46" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>681</v>
       </c>
       <c r="R46" s="4">
         <f>S46</f>
         <v>800</v>
       </c>
-      <c r="S46" s="19">
+      <c r="S46" s="8">
         <f>VLOOKUP(A46,[1]Sheet!$A:$R,18,0)</f>
         <v>800</v>
       </c>
@@ -10925,7 +11039,7 @@
         <v>16.483790523690772</v>
       </c>
       <c r="U46" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.508728179551122</v>
       </c>
       <c r="V46" s="8">
@@ -10963,7 +11077,10 @@
         <f t="shared" si="7"/>
         <v>280</v>
       </c>
-      <c r="AH46" s="8"/>
+      <c r="AH46" s="8">
+        <f t="shared" si="8"/>
+        <v>28.07</v>
+      </c>
       <c r="AI46" s="8"/>
       <c r="AJ46" s="8"/>
       <c r="AK46" s="8"/>
@@ -11014,7 +11131,7 @@
         <v>137</v>
       </c>
       <c r="L47" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-24</v>
       </c>
       <c r="M47" s="8"/>
@@ -11023,24 +11140,24 @@
         <v>0</v>
       </c>
       <c r="P47" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>22.6</v>
       </c>
       <c r="Q47" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>24</v>
       </c>
       <c r="R47" s="4">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="S47" s="19"/>
+      <c r="S47" s="8"/>
       <c r="T47" s="8">
         <f t="shared" si="6"/>
         <v>14.999999999999998</v>
       </c>
       <c r="U47" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.938053097345131</v>
       </c>
       <c r="V47" s="8">
@@ -11078,7 +11195,10 @@
         <f t="shared" si="7"/>
         <v>9.84</v>
       </c>
-      <c r="AH47" s="8"/>
+      <c r="AH47" s="8">
+        <f t="shared" si="8"/>
+        <v>9.266</v>
+      </c>
       <c r="AI47" s="8"/>
       <c r="AJ47" s="8"/>
       <c r="AK47" s="8"/>
@@ -11129,7 +11249,7 @@
         <v>123</v>
       </c>
       <c r="L48" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-34</v>
       </c>
       <c r="M48" s="8"/>
@@ -11138,14 +11258,14 @@
         <v>218</v>
       </c>
       <c r="P48" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>17.8</v>
       </c>
       <c r="Q48" s="4"/>
       <c r="R48" s="4">
         <v>100</v>
       </c>
-      <c r="S48" s="19">
+      <c r="S48" s="8">
         <f>VLOOKUP(A48,[1]Sheet!$A:$R,18,0)</f>
         <v>150</v>
       </c>
@@ -11154,7 +11274,7 @@
         <v>31.235955056179773</v>
       </c>
       <c r="U48" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>25.617977528089888</v>
       </c>
       <c r="V48" s="8">
@@ -11192,7 +11312,10 @@
         <f t="shared" si="7"/>
         <v>41</v>
       </c>
-      <c r="AH48" s="8"/>
+      <c r="AH48" s="8">
+        <f t="shared" si="8"/>
+        <v>7.298</v>
+      </c>
       <c r="AI48" s="8"/>
       <c r="AJ48" s="8"/>
       <c r="AK48" s="8"/>
@@ -11243,7 +11366,7 @@
         <v>59</v>
       </c>
       <c r="L49" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-4</v>
       </c>
       <c r="M49" s="8"/>
@@ -11252,7 +11375,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>11</v>
       </c>
       <c r="Q49" s="4"/>
@@ -11260,13 +11383,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S49" s="19"/>
+      <c r="S49" s="8"/>
       <c r="T49" s="8">
         <f t="shared" si="6"/>
         <v>21.818181818181817</v>
       </c>
       <c r="U49" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>21.818181818181817</v>
       </c>
       <c r="V49" s="8">
@@ -11299,14 +11422,17 @@
       <c r="AE49" s="8">
         <v>26.6</v>
       </c>
-      <c r="AF49" s="16" t="s">
+      <c r="AF49" s="15" t="s">
         <v>40</v>
       </c>
       <c r="AG49" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH49" s="8"/>
+      <c r="AH49" s="8">
+        <f t="shared" si="8"/>
+        <v>3.96</v>
+      </c>
       <c r="AI49" s="8"/>
       <c r="AJ49" s="8"/>
       <c r="AK49" s="8"/>
@@ -11355,7 +11481,7 @@
         <v>57</v>
       </c>
       <c r="L50" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-19</v>
       </c>
       <c r="M50" s="8"/>
@@ -11364,17 +11490,17 @@
         <v>97</v>
       </c>
       <c r="P50" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.6</v>
       </c>
       <c r="Q50" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>17</v>
       </c>
       <c r="R50" s="4">
         <v>60</v>
       </c>
-      <c r="S50" s="19">
+      <c r="S50" s="8">
         <f>VLOOKUP(A50,[1]Sheet!$A:$R,18,0)</f>
         <v>80</v>
       </c>
@@ -11383,7 +11509,7 @@
         <v>20.657894736842106</v>
       </c>
       <c r="U50" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>12.763157894736842</v>
       </c>
       <c r="V50" s="8">
@@ -11423,7 +11549,10 @@
         <f t="shared" si="7"/>
         <v>19.8</v>
       </c>
-      <c r="AH50" s="8"/>
+      <c r="AH50" s="8">
+        <f t="shared" si="8"/>
+        <v>2.508</v>
+      </c>
       <c r="AI50" s="8"/>
       <c r="AJ50" s="8"/>
       <c r="AK50" s="8"/>
@@ -11474,7 +11603,7 @@
         <v>68</v>
       </c>
       <c r="L51" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="M51" s="8"/>
@@ -11483,17 +11612,17 @@
         <v>157</v>
       </c>
       <c r="P51" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13.8</v>
       </c>
       <c r="Q51" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>25</v>
       </c>
       <c r="R51" s="4">
         <v>80</v>
       </c>
-      <c r="S51" s="19">
+      <c r="S51" s="8">
         <f>VLOOKUP(A51,[1]Sheet!$A:$R,18,0)</f>
         <v>100</v>
       </c>
@@ -11502,7 +11631,7 @@
         <v>18.985507246376809</v>
       </c>
       <c r="U51" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.188405797101449</v>
       </c>
       <c r="V51" s="8">
@@ -11540,7 +11669,10 @@
         <f t="shared" si="7"/>
         <v>32</v>
       </c>
-      <c r="AH51" s="8"/>
+      <c r="AH51" s="8">
+        <f t="shared" si="8"/>
+        <v>5.5200000000000005</v>
+      </c>
       <c r="AI51" s="8"/>
       <c r="AJ51" s="8"/>
       <c r="AK51" s="8"/>
@@ -11591,7 +11723,7 @@
         <v>58</v>
       </c>
       <c r="L52" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-16</v>
       </c>
       <c r="M52" s="8"/>
@@ -11600,17 +11732,17 @@
         <v>47</v>
       </c>
       <c r="P52" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.4</v>
       </c>
       <c r="Q52" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>46</v>
       </c>
       <c r="R52" s="4">
         <v>80</v>
       </c>
-      <c r="S52" s="19">
+      <c r="S52" s="8">
         <f>VLOOKUP(A52,[1]Sheet!$A:$R,18,0)</f>
         <v>90</v>
       </c>
@@ -11619,7 +11751,7 @@
         <v>19.047619047619047</v>
       </c>
       <c r="U52" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.5238095238095237</v>
       </c>
       <c r="V52" s="8">
@@ -11657,7 +11789,10 @@
         <f t="shared" si="7"/>
         <v>26.400000000000002</v>
       </c>
-      <c r="AH52" s="8"/>
+      <c r="AH52" s="8">
+        <f t="shared" si="8"/>
+        <v>2.7720000000000002</v>
+      </c>
       <c r="AI52" s="8"/>
       <c r="AJ52" s="8"/>
       <c r="AK52" s="8"/>
@@ -11708,7 +11843,7 @@
         <v>342</v>
       </c>
       <c r="L53" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>29.204999999999984</v>
       </c>
       <c r="M53" s="8"/>
@@ -11717,18 +11852,18 @@
         <v>0</v>
       </c>
       <c r="P53" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>74.241</v>
       </c>
       <c r="Q53" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>586.66100000000006</v>
       </c>
       <c r="R53" s="4">
-        <f t="shared" ref="R50:R53" si="17">S53</f>
+        <f t="shared" ref="R53" si="18">S53</f>
         <v>700</v>
       </c>
-      <c r="S53" s="19">
+      <c r="S53" s="8">
         <f>VLOOKUP(A53,[1]Sheet!$A:$R,18,0)</f>
         <v>700</v>
       </c>
@@ -11737,7 +11872,7 @@
         <v>16.526636225266362</v>
       </c>
       <c r="U53" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.0978839185894582</v>
       </c>
       <c r="V53" s="8">
@@ -11775,7 +11910,10 @@
         <f t="shared" si="7"/>
         <v>700</v>
       </c>
-      <c r="AH53" s="8"/>
+      <c r="AH53" s="8">
+        <f t="shared" si="8"/>
+        <v>74.241</v>
+      </c>
       <c r="AI53" s="8"/>
       <c r="AJ53" s="8"/>
       <c r="AK53" s="8"/>
@@ -11794,98 +11932,101 @@
       <c r="AX53" s="8"/>
     </row>
     <row r="54" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C54" s="11">
+      <c r="C54" s="10">
         <v>-1</v>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="10">
         <v>1</v>
       </c>
-      <c r="E54" s="11">
+      <c r="E54" s="10">
         <v>-2</v>
       </c>
-      <c r="F54" s="11"/>
-      <c r="G54" s="12">
-        <v>0</v>
-      </c>
-      <c r="H54" s="11">
+      <c r="F54" s="10"/>
+      <c r="G54" s="11">
+        <v>0</v>
+      </c>
+      <c r="H54" s="10">
         <v>60</v>
       </c>
-      <c r="I54" s="11" t="s">
+      <c r="I54" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J54" s="11"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11">
-        <f t="shared" si="12"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10">
+        <f t="shared" si="13"/>
         <v>-2</v>
       </c>
-      <c r="M54" s="11"/>
-      <c r="N54" s="11"/>
-      <c r="O54" s="11">
-        <v>0</v>
-      </c>
-      <c r="P54" s="11">
-        <f t="shared" si="13"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="10">
+        <v>0</v>
+      </c>
+      <c r="P54" s="10">
+        <f t="shared" si="14"/>
         <v>-0.4</v>
       </c>
-      <c r="Q54" s="13"/>
+      <c r="Q54" s="12"/>
       <c r="R54" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S54" s="19"/>
+      <c r="S54" s="8"/>
       <c r="T54" s="8">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U54" s="11">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="V54" s="11">
+      <c r="U54" s="10">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="10">
         <v>-0.2</v>
       </c>
-      <c r="W54" s="11">
-        <v>0</v>
-      </c>
-      <c r="X54" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y54" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA54" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB54" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC54" s="11">
+      <c r="W54" s="10">
+        <v>0</v>
+      </c>
+      <c r="X54" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="10">
         <v>-0.2</v>
       </c>
-      <c r="AD54" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE54" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF54" s="11" t="s">
+      <c r="AD54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="10" t="s">
         <v>98</v>
       </c>
       <c r="AG54" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH54" s="8"/>
+      <c r="AH54" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI54" s="8"/>
       <c r="AJ54" s="8"/>
       <c r="AK54" s="8"/>
@@ -11934,7 +12075,7 @@
         <v>54</v>
       </c>
       <c r="L55" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-34</v>
       </c>
       <c r="M55" s="8"/>
@@ -11943,24 +12084,24 @@
         <v>0</v>
       </c>
       <c r="P55" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="Q55" s="4">
-        <f t="shared" ref="Q55:Q56" si="18">8*P55-O55-F55</f>
+        <f t="shared" ref="Q55:Q56" si="19">8*P55-O55-F55</f>
         <v>32</v>
       </c>
       <c r="R55" s="4">
         <f t="shared" si="5"/>
         <v>32</v>
       </c>
-      <c r="S55" s="19"/>
+      <c r="S55" s="8"/>
       <c r="T55" s="8">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="U55" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V55" s="8">
@@ -11998,7 +12139,10 @@
         <f t="shared" si="7"/>
         <v>12.8</v>
       </c>
-      <c r="AH55" s="8"/>
+      <c r="AH55" s="8">
+        <f t="shared" si="8"/>
+        <v>1.6</v>
+      </c>
       <c r="AI55" s="8"/>
       <c r="AJ55" s="8"/>
       <c r="AK55" s="8"/>
@@ -12047,7 +12191,7 @@
         <v>6</v>
       </c>
       <c r="L56" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.7690000000000001</v>
       </c>
       <c r="M56" s="8"/>
@@ -12056,24 +12200,24 @@
         <v>0</v>
       </c>
       <c r="P56" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.5538000000000001</v>
       </c>
       <c r="Q56" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>12.430400000000001</v>
       </c>
       <c r="R56" s="4">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="S56" s="19"/>
+      <c r="S56" s="8"/>
       <c r="T56" s="8">
         <f t="shared" si="6"/>
         <v>7.7230016733170288</v>
       </c>
       <c r="U56" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V56" s="8">
@@ -12111,7 +12255,10 @@
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
-      <c r="AH56" s="8"/>
+      <c r="AH56" s="8">
+        <f t="shared" si="8"/>
+        <v>1.5538000000000001</v>
+      </c>
       <c r="AI56" s="8"/>
       <c r="AJ56" s="8"/>
       <c r="AK56" s="8"/>
@@ -12130,94 +12277,97 @@
       <c r="AX56" s="8"/>
     </row>
     <row r="57" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C57" s="11">
+      <c r="C57" s="10">
         <v>3.8809999999999998</v>
       </c>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="12">
-        <v>0</v>
-      </c>
-      <c r="H57" s="11">
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="11">
+        <v>0</v>
+      </c>
+      <c r="H57" s="10">
         <v>60</v>
       </c>
-      <c r="I57" s="11" t="s">
+      <c r="I57" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J57" s="11"/>
-      <c r="K57" s="11">
+      <c r="J57" s="10"/>
+      <c r="K57" s="10">
         <v>6</v>
       </c>
-      <c r="L57" s="11">
-        <f t="shared" si="12"/>
+      <c r="L57" s="10">
+        <f t="shared" si="13"/>
         <v>-6</v>
       </c>
-      <c r="M57" s="11"/>
-      <c r="N57" s="11"/>
-      <c r="O57" s="11">
-        <v>0</v>
-      </c>
-      <c r="P57" s="11">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Q57" s="13"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="10">
+        <v>0</v>
+      </c>
+      <c r="P57" s="10">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="Q57" s="12"/>
       <c r="R57" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S57" s="19"/>
+      <c r="S57" s="8"/>
       <c r="T57" s="8" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U57" s="11" t="e">
-        <f t="shared" si="14"/>
+      <c r="U57" s="10" t="e">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V57" s="11">
-        <v>0</v>
-      </c>
-      <c r="W57" s="11">
-        <v>0</v>
-      </c>
-      <c r="X57" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC57" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF57" s="11"/>
+      <c r="V57" s="10">
+        <v>0</v>
+      </c>
+      <c r="W57" s="10">
+        <v>0</v>
+      </c>
+      <c r="X57" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="10"/>
       <c r="AG57" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH57" s="8"/>
+      <c r="AH57" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI57" s="8"/>
       <c r="AJ57" s="8"/>
       <c r="AK57" s="8"/>
@@ -12266,7 +12416,7 @@
         <v>66</v>
       </c>
       <c r="L58" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1.0250000000000057</v>
       </c>
       <c r="M58" s="8"/>
@@ -12275,7 +12425,7 @@
         <v>0</v>
       </c>
       <c r="P58" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>12.994999999999999</v>
       </c>
       <c r="Q58" s="4">
@@ -12286,13 +12436,13 @@
         <f t="shared" si="5"/>
         <v>104</v>
       </c>
-      <c r="S58" s="19"/>
+      <c r="S58" s="8"/>
       <c r="T58" s="8">
         <f t="shared" si="6"/>
         <v>8.0030781069642174</v>
       </c>
       <c r="U58" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V58" s="8">
@@ -12330,7 +12480,10 @@
         <f t="shared" si="7"/>
         <v>104</v>
       </c>
-      <c r="AH58" s="8"/>
+      <c r="AH58" s="8">
+        <f t="shared" si="8"/>
+        <v>12.994999999999999</v>
+      </c>
       <c r="AI58" s="8"/>
       <c r="AJ58" s="8"/>
       <c r="AK58" s="8"/>
@@ -12379,7 +12532,7 @@
         <v>3.004</v>
       </c>
       <c r="L59" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.1339999999999999</v>
       </c>
       <c r="M59" s="8"/>
@@ -12388,7 +12541,7 @@
         <v>0</v>
       </c>
       <c r="P59" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.62759999999999994</v>
       </c>
       <c r="Q59" s="4"/>
@@ -12396,13 +12549,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S59" s="19"/>
+      <c r="S59" s="8"/>
       <c r="T59" s="8">
         <f t="shared" si="6"/>
         <v>150.25493945188018</v>
       </c>
       <c r="U59" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>150.25493945188018</v>
       </c>
       <c r="V59" s="8">
@@ -12442,7 +12595,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH59" s="8"/>
+      <c r="AH59" s="8">
+        <f t="shared" si="8"/>
+        <v>0.62759999999999994</v>
+      </c>
       <c r="AI59" s="8"/>
       <c r="AJ59" s="8"/>
       <c r="AK59" s="8"/>
@@ -12493,7 +12649,7 @@
         <v>29</v>
       </c>
       <c r="L60" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-9</v>
       </c>
       <c r="M60" s="8"/>
@@ -12502,7 +12658,7 @@
         <v>55</v>
       </c>
       <c r="P60" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="Q60" s="4"/>
@@ -12510,13 +12666,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S60" s="19"/>
+      <c r="S60" s="8"/>
       <c r="T60" s="8">
         <f t="shared" si="6"/>
         <v>16.5</v>
       </c>
       <c r="U60" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>16.5</v>
       </c>
       <c r="V60" s="8">
@@ -12556,7 +12712,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH60" s="8"/>
+      <c r="AH60" s="8">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
       <c r="AI60" s="8"/>
       <c r="AJ60" s="8"/>
       <c r="AK60" s="8"/>
@@ -12607,7 +12766,7 @@
         <v>61.3</v>
       </c>
       <c r="L61" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.4030000000000058</v>
       </c>
       <c r="M61" s="8"/>
@@ -12616,17 +12775,17 @@
         <v>47</v>
       </c>
       <c r="P61" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13.140600000000001</v>
       </c>
       <c r="Q61" s="4">
-        <f t="shared" ref="Q61:Q70" si="19">15*P61-O61-F61</f>
+        <f t="shared" ref="Q61:Q70" si="20">15*P61-O61-F61</f>
         <v>99.207000000000008</v>
       </c>
       <c r="R61" s="4">
         <v>150</v>
       </c>
-      <c r="S61" s="19">
+      <c r="S61" s="8">
         <f>VLOOKUP(A61,[1]Sheet!$A:$R,18,0)</f>
         <v>180</v>
       </c>
@@ -12635,7 +12794,7 @@
         <v>18.865348614218526</v>
       </c>
       <c r="U61" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.450344733117209</v>
       </c>
       <c r="V61" s="8">
@@ -12673,7 +12832,10 @@
         <f t="shared" si="7"/>
         <v>150</v>
       </c>
-      <c r="AH61" s="8"/>
+      <c r="AH61" s="8">
+        <f t="shared" si="8"/>
+        <v>13.140600000000001</v>
+      </c>
       <c r="AI61" s="8"/>
       <c r="AJ61" s="8"/>
       <c r="AK61" s="8"/>
@@ -12722,7 +12884,7 @@
         <v>116</v>
       </c>
       <c r="L62" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-58</v>
       </c>
       <c r="M62" s="8"/>
@@ -12731,17 +12893,17 @@
         <v>19</v>
       </c>
       <c r="P62" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>11.6</v>
       </c>
       <c r="Q62" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>43</v>
       </c>
       <c r="R62" s="4">
         <v>100</v>
       </c>
-      <c r="S62" s="19">
+      <c r="S62" s="8">
         <f>VLOOKUP(A62,[1]Sheet!$A:$R,18,0)</f>
         <v>150</v>
       </c>
@@ -12750,7 +12912,7 @@
         <v>19.913793103448278</v>
       </c>
       <c r="U62" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>11.293103448275863</v>
       </c>
       <c r="V62" s="8">
@@ -12790,7 +12952,10 @@
         <f t="shared" si="7"/>
         <v>27</v>
       </c>
-      <c r="AH62" s="8"/>
+      <c r="AH62" s="8">
+        <f t="shared" si="8"/>
+        <v>3.1320000000000001</v>
+      </c>
       <c r="AI62" s="8"/>
       <c r="AJ62" s="8"/>
       <c r="AK62" s="8"/>
@@ -12841,7 +13006,7 @@
         <v>55</v>
       </c>
       <c r="L63" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-45</v>
       </c>
       <c r="M63" s="8"/>
@@ -12850,7 +13015,7 @@
         <v>60</v>
       </c>
       <c r="P63" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="Q63" s="4"/>
@@ -12858,13 +13023,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S63" s="19"/>
+      <c r="S63" s="8"/>
       <c r="T63" s="8">
         <f t="shared" si="6"/>
         <v>62</v>
       </c>
       <c r="U63" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>62</v>
       </c>
       <c r="V63" s="8">
@@ -12897,14 +13062,17 @@
       <c r="AE63" s="8">
         <v>4.2</v>
       </c>
-      <c r="AF63" s="18" t="s">
+      <c r="AF63" s="17" t="s">
         <v>172</v>
       </c>
       <c r="AG63" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH63" s="8"/>
+      <c r="AH63" s="8">
+        <f t="shared" si="8"/>
+        <v>0.6</v>
+      </c>
       <c r="AI63" s="8"/>
       <c r="AJ63" s="8"/>
       <c r="AK63" s="8"/>
@@ -12938,7 +13106,7 @@
       <c r="E64" s="8">
         <v>259</v>
       </c>
-      <c r="F64" s="15">
+      <c r="F64" s="14">
         <f>904+F119</f>
         <v>933</v>
       </c>
@@ -12956,7 +13124,7 @@
         <v>252</v>
       </c>
       <c r="L64" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7</v>
       </c>
       <c r="M64" s="8"/>
@@ -12965,7 +13133,7 @@
         <v>0</v>
       </c>
       <c r="P64" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>51.8</v>
       </c>
       <c r="Q64" s="4"/>
@@ -12973,13 +13141,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S64" s="19"/>
+      <c r="S64" s="8"/>
       <c r="T64" s="8">
         <f t="shared" si="6"/>
         <v>18.011583011583014</v>
       </c>
       <c r="U64" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>18.011583011583014</v>
       </c>
       <c r="V64" s="8">
@@ -13012,14 +13180,17 @@
       <c r="AE64" s="8">
         <v>77.2</v>
       </c>
-      <c r="AF64" s="10" t="s">
+      <c r="AF64" s="9" t="s">
         <v>73</v>
       </c>
       <c r="AG64" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH64" s="8"/>
+      <c r="AH64" s="8">
+        <f t="shared" si="8"/>
+        <v>21.237999999999996</v>
+      </c>
       <c r="AI64" s="8"/>
       <c r="AJ64" s="8"/>
       <c r="AK64" s="8"/>
@@ -13070,7 +13241,7 @@
         <v>156.30000000000001</v>
       </c>
       <c r="L65" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>9.7379999999999995</v>
       </c>
       <c r="M65" s="8"/>
@@ -13079,18 +13250,18 @@
         <v>120</v>
       </c>
       <c r="P65" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>33.207599999999999</v>
       </c>
       <c r="Q65" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>262.10599999999999</v>
       </c>
       <c r="R65" s="4">
         <f>S65</f>
         <v>400</v>
       </c>
-      <c r="S65" s="19">
+      <c r="S65" s="8">
         <f>VLOOKUP(A65,[1]Sheet!$A:$R,18,0)</f>
         <v>400</v>
       </c>
@@ -13099,7 +13270,7 @@
         <v>19.152483166504055</v>
       </c>
       <c r="U65" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.1070477842421607</v>
       </c>
       <c r="V65" s="8">
@@ -13137,7 +13308,10 @@
         <f t="shared" si="7"/>
         <v>400</v>
       </c>
-      <c r="AH65" s="8"/>
+      <c r="AH65" s="8">
+        <f t="shared" si="8"/>
+        <v>33.207599999999999</v>
+      </c>
       <c r="AI65" s="8"/>
       <c r="AJ65" s="8"/>
       <c r="AK65" s="8"/>
@@ -13188,7 +13362,7 @@
         <v>71</v>
       </c>
       <c r="L66" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-5</v>
       </c>
       <c r="M66" s="8"/>
@@ -13197,7 +13371,7 @@
         <v>196</v>
       </c>
       <c r="P66" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13.2</v>
       </c>
       <c r="Q66" s="4"/>
@@ -13205,13 +13379,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S66" s="19"/>
+      <c r="S66" s="8"/>
       <c r="T66" s="8">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="U66" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15</v>
       </c>
       <c r="V66" s="8">
@@ -13249,7 +13423,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH66" s="8"/>
+      <c r="AH66" s="8">
+        <f t="shared" si="8"/>
+        <v>4.6199999999999992</v>
+      </c>
       <c r="AI66" s="8"/>
       <c r="AJ66" s="8"/>
       <c r="AK66" s="8"/>
@@ -13300,7 +13477,7 @@
         <v>26.5</v>
       </c>
       <c r="L67" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.3619999999999983</v>
       </c>
       <c r="M67" s="8"/>
@@ -13309,7 +13486,7 @@
         <v>64</v>
       </c>
       <c r="P67" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.5724</v>
       </c>
       <c r="Q67" s="4"/>
@@ -13317,13 +13494,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S67" s="19"/>
+      <c r="S67" s="8"/>
       <c r="T67" s="8">
         <f t="shared" si="6"/>
         <v>17.048309525518629</v>
       </c>
       <c r="U67" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>17.048309525518629</v>
       </c>
       <c r="V67" s="8">
@@ -13361,7 +13538,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH67" s="8"/>
+      <c r="AH67" s="8">
+        <f t="shared" si="8"/>
+        <v>5.5724</v>
+      </c>
       <c r="AI67" s="8"/>
       <c r="AJ67" s="8"/>
       <c r="AK67" s="8"/>
@@ -13412,7 +13592,7 @@
         <v>86</v>
       </c>
       <c r="L68" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-36</v>
       </c>
       <c r="M68" s="8"/>
@@ -13421,7 +13601,7 @@
         <v>0</v>
       </c>
       <c r="P68" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10</v>
       </c>
       <c r="Q68" s="4"/>
@@ -13429,13 +13609,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S68" s="19"/>
+      <c r="S68" s="8"/>
       <c r="T68" s="8">
         <f t="shared" si="6"/>
         <v>55</v>
       </c>
       <c r="U68" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>55</v>
       </c>
       <c r="V68" s="8">
@@ -13473,7 +13653,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH68" s="8"/>
+      <c r="AH68" s="8">
+        <f t="shared" si="8"/>
+        <v>4.0999999999999996</v>
+      </c>
       <c r="AI68" s="8"/>
       <c r="AJ68" s="8"/>
       <c r="AK68" s="8"/>
@@ -13524,7 +13707,7 @@
         <v>134</v>
       </c>
       <c r="L69" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.1049999999999898</v>
       </c>
       <c r="M69" s="8"/>
@@ -13533,7 +13716,7 @@
         <v>0</v>
       </c>
       <c r="P69" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>28.220999999999997</v>
       </c>
       <c r="Q69" s="4">
@@ -13541,10 +13724,10 @@
         <v>230.95299999999995</v>
       </c>
       <c r="R69" s="4">
-        <f t="shared" ref="R69:R70" si="20">S69</f>
+        <f t="shared" ref="R69" si="21">S69</f>
         <v>350</v>
       </c>
-      <c r="S69" s="19">
+      <c r="S69" s="8">
         <f>VLOOKUP(A69,[1]Sheet!$A:$R,18,0)</f>
         <v>350</v>
       </c>
@@ -13553,7 +13736,7 @@
         <v>18.218383473300026</v>
       </c>
       <c r="U69" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.8162715708160597</v>
       </c>
       <c r="V69" s="8">
@@ -13591,7 +13774,10 @@
         <f t="shared" si="7"/>
         <v>350</v>
       </c>
-      <c r="AH69" s="8"/>
+      <c r="AH69" s="8">
+        <f t="shared" si="8"/>
+        <v>28.220999999999997</v>
+      </c>
       <c r="AI69" s="8"/>
       <c r="AJ69" s="8"/>
       <c r="AK69" s="8"/>
@@ -13642,7 +13828,7 @@
         <v>70</v>
       </c>
       <c r="L70" s="8">
-        <f t="shared" ref="L70:L101" si="21">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="22">E70-K70</f>
         <v>-5</v>
       </c>
       <c r="M70" s="8"/>
@@ -13651,17 +13837,17 @@
         <v>0</v>
       </c>
       <c r="P70" s="8">
-        <f t="shared" ref="P70:P101" si="22">E70/5</f>
+        <f t="shared" ref="P70:P101" si="23">E70/5</f>
         <v>13</v>
       </c>
       <c r="Q70" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>69</v>
       </c>
       <c r="R70" s="4">
         <v>120</v>
       </c>
-      <c r="S70" s="19">
+      <c r="S70" s="8">
         <f>VLOOKUP(A70,[1]Sheet!$A:$R,18,0)</f>
         <v>150</v>
       </c>
@@ -13670,7 +13856,7 @@
         <v>18.923076923076923</v>
       </c>
       <c r="U70" s="8">
-        <f t="shared" ref="U70:U101" si="23">(F70+O70)/P70</f>
+        <f t="shared" ref="U70:U101" si="24">(F70+O70)/P70</f>
         <v>9.6923076923076916</v>
       </c>
       <c r="V70" s="8">
@@ -13708,7 +13894,10 @@
         <f t="shared" si="7"/>
         <v>36</v>
       </c>
-      <c r="AH70" s="8"/>
+      <c r="AH70" s="8">
+        <f t="shared" si="8"/>
+        <v>3.9</v>
+      </c>
       <c r="AI70" s="8"/>
       <c r="AJ70" s="8"/>
       <c r="AK70" s="8"/>
@@ -13727,98 +13916,101 @@
       <c r="AX70" s="8"/>
     </row>
     <row r="71" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A71" s="11" t="s">
+      <c r="A71" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B71" s="11" t="s">
+      <c r="B71" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C71" s="11">
+      <c r="C71" s="10">
         <v>2</v>
       </c>
-      <c r="D71" s="11">
+      <c r="D71" s="10">
         <v>8</v>
       </c>
-      <c r="E71" s="11">
+      <c r="E71" s="10">
         <v>-4</v>
       </c>
-      <c r="F71" s="11"/>
-      <c r="G71" s="12">
-        <v>0</v>
-      </c>
-      <c r="H71" s="11">
+      <c r="F71" s="10"/>
+      <c r="G71" s="11">
+        <v>0</v>
+      </c>
+      <c r="H71" s="10">
         <v>50</v>
       </c>
-      <c r="I71" s="11" t="s">
+      <c r="I71" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J71" s="11"/>
-      <c r="K71" s="11">
+      <c r="J71" s="10"/>
+      <c r="K71" s="10">
         <v>11</v>
       </c>
-      <c r="L71" s="11">
-        <f t="shared" si="21"/>
+      <c r="L71" s="10">
+        <f t="shared" si="22"/>
         <v>-15</v>
       </c>
-      <c r="M71" s="11"/>
-      <c r="N71" s="11"/>
-      <c r="O71" s="11">
-        <v>0</v>
-      </c>
-      <c r="P71" s="11">
-        <f t="shared" si="22"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="10">
+        <v>0</v>
+      </c>
+      <c r="P71" s="10">
+        <f t="shared" si="23"/>
         <v>-0.8</v>
       </c>
-      <c r="Q71" s="13"/>
+      <c r="Q71" s="12"/>
       <c r="R71" s="4">
-        <f t="shared" ref="R71:R119" si="24">ROUND(Q71,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S71" s="19"/>
+        <f t="shared" ref="R71:R119" si="25">ROUND(Q71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S71" s="8"/>
       <c r="T71" s="8">
-        <f t="shared" ref="T71:T119" si="25">(F71+O71+R71)/P71</f>
-        <v>0</v>
-      </c>
-      <c r="U71" s="11">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="V71" s="11">
-        <v>0</v>
-      </c>
-      <c r="W71" s="11">
-        <v>0</v>
-      </c>
-      <c r="X71" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y71" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z71" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA71" s="11">
+        <f t="shared" ref="T71:T119" si="26">(F71+O71+R71)/P71</f>
+        <v>0</v>
+      </c>
+      <c r="U71" s="10">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="V71" s="10">
+        <v>0</v>
+      </c>
+      <c r="W71" s="10">
+        <v>0</v>
+      </c>
+      <c r="X71" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="10">
         <v>0.6</v>
       </c>
-      <c r="AB71" s="11">
+      <c r="AB71" s="10">
         <v>0.4</v>
       </c>
-      <c r="AC71" s="11">
+      <c r="AC71" s="10">
         <v>8.6</v>
       </c>
-      <c r="AD71" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE71" s="11">
+      <c r="AD71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="10">
         <v>1.8</v>
       </c>
-      <c r="AF71" s="11"/>
+      <c r="AF71" s="10"/>
       <c r="AG71" s="8">
-        <f t="shared" ref="AG71:AG119" si="26">G71*R71</f>
-        <v>0</v>
-      </c>
-      <c r="AH71" s="8"/>
+        <f t="shared" ref="AG71:AG119" si="27">G71*R71</f>
+        <v>0</v>
+      </c>
+      <c r="AH71" s="8">
+        <f t="shared" ref="AH71:AH119" si="28">P71*G71</f>
+        <v>0</v>
+      </c>
       <c r="AI71" s="8"/>
       <c r="AJ71" s="8"/>
       <c r="AK71" s="8"/>
@@ -13869,7 +14061,7 @@
         <v>137</v>
       </c>
       <c r="L72" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-22</v>
       </c>
       <c r="M72" s="8"/>
@@ -13878,21 +14070,21 @@
         <v>0</v>
       </c>
       <c r="P72" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>23</v>
       </c>
       <c r="Q72" s="4"/>
       <c r="R72" s="4">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S72" s="8"/>
+      <c r="T72" s="8">
+        <f t="shared" si="26"/>
+        <v>24.521739130434781</v>
+      </c>
+      <c r="U72" s="8">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S72" s="19"/>
-      <c r="T72" s="8">
-        <f t="shared" si="25"/>
-        <v>24.521739130434781</v>
-      </c>
-      <c r="U72" s="8">
-        <f t="shared" si="23"/>
         <v>24.521739130434781</v>
       </c>
       <c r="V72" s="8">
@@ -13925,14 +14117,17 @@
       <c r="AE72" s="8">
         <v>36.6</v>
       </c>
-      <c r="AF72" s="10" t="s">
+      <c r="AF72" s="9" t="s">
         <v>73</v>
       </c>
       <c r="AG72" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH72" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH72" s="8">
+        <f t="shared" si="28"/>
+        <v>4.1399999999999997</v>
+      </c>
       <c r="AI72" s="8"/>
       <c r="AJ72" s="8"/>
       <c r="AK72" s="8"/>
@@ -13981,7 +14176,7 @@
         <v>10</v>
       </c>
       <c r="L73" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M73" s="8"/>
@@ -13990,21 +14185,21 @@
         <v>0</v>
       </c>
       <c r="P73" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2</v>
       </c>
       <c r="Q73" s="4"/>
       <c r="R73" s="4">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S73" s="8"/>
+      <c r="T73" s="8">
+        <f t="shared" si="26"/>
+        <v>39</v>
+      </c>
+      <c r="U73" s="8">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S73" s="19"/>
-      <c r="T73" s="8">
-        <f t="shared" si="25"/>
-        <v>39</v>
-      </c>
-      <c r="U73" s="8">
-        <f t="shared" si="23"/>
         <v>39</v>
       </c>
       <c r="V73" s="8">
@@ -14041,10 +14236,13 @@
         <v>37</v>
       </c>
       <c r="AG73" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH73" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH73" s="8">
+        <f t="shared" si="28"/>
+        <v>0.44</v>
+      </c>
       <c r="AI73" s="8"/>
       <c r="AJ73" s="8"/>
       <c r="AK73" s="8"/>
@@ -14095,7 +14293,7 @@
         <v>23.5</v>
       </c>
       <c r="L74" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1.5</v>
       </c>
       <c r="M74" s="8"/>
@@ -14104,23 +14302,23 @@
         <v>61</v>
       </c>
       <c r="P74" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5</v>
       </c>
       <c r="Q74" s="4">
         <v>6</v>
       </c>
       <c r="R74" s="4">
+        <f t="shared" si="25"/>
+        <v>6</v>
+      </c>
+      <c r="S74" s="8"/>
+      <c r="T74" s="8">
+        <f t="shared" si="26"/>
+        <v>15.4</v>
+      </c>
+      <c r="U74" s="8">
         <f t="shared" si="24"/>
-        <v>6</v>
-      </c>
-      <c r="S74" s="19"/>
-      <c r="T74" s="8">
-        <f t="shared" si="25"/>
-        <v>15.4</v>
-      </c>
-      <c r="U74" s="8">
-        <f t="shared" si="23"/>
         <v>14.2</v>
       </c>
       <c r="V74" s="8">
@@ -14155,10 +14353,13 @@
       </c>
       <c r="AF74" s="8"/>
       <c r="AG74" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>5.04</v>
       </c>
-      <c r="AH74" s="8"/>
+      <c r="AH74" s="8">
+        <f t="shared" si="28"/>
+        <v>4.2</v>
+      </c>
       <c r="AI74" s="8"/>
       <c r="AJ74" s="8"/>
       <c r="AK74" s="8"/>
@@ -14209,7 +14410,7 @@
         <v>334</v>
       </c>
       <c r="L75" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-18</v>
       </c>
       <c r="M75" s="8"/>
@@ -14218,27 +14419,27 @@
         <v>0</v>
       </c>
       <c r="P75" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>63.2</v>
       </c>
       <c r="Q75" s="4">
-        <f t="shared" ref="Q75" si="27">15*P75-O75-F75</f>
+        <f t="shared" ref="Q75" si="29">15*P75-O75-F75</f>
         <v>289</v>
       </c>
       <c r="R75" s="4">
         <f>S75</f>
         <v>400</v>
       </c>
-      <c r="S75" s="19">
+      <c r="S75" s="8">
         <f>VLOOKUP(A75,[1]Sheet!$A:$R,18,0)</f>
         <v>400</v>
       </c>
       <c r="T75" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>16.75632911392405</v>
       </c>
       <c r="U75" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>10.427215189873417</v>
       </c>
       <c r="V75" s="8">
@@ -14273,10 +14474,13 @@
       </c>
       <c r="AF75" s="8"/>
       <c r="AG75" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>140</v>
       </c>
-      <c r="AH75" s="8"/>
+      <c r="AH75" s="8">
+        <f t="shared" si="28"/>
+        <v>22.12</v>
+      </c>
       <c r="AI75" s="8"/>
       <c r="AJ75" s="8"/>
       <c r="AK75" s="8"/>
@@ -14295,90 +14499,93 @@
       <c r="AX75" s="8"/>
     </row>
     <row r="76" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C76" s="11"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="12">
-        <v>0</v>
-      </c>
-      <c r="H76" s="11"/>
-      <c r="I76" s="11" t="s">
+      <c r="C76" s="10"/>
+      <c r="D76" s="10"/>
+      <c r="E76" s="10"/>
+      <c r="F76" s="10"/>
+      <c r="G76" s="11">
+        <v>0</v>
+      </c>
+      <c r="H76" s="10"/>
+      <c r="I76" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J76" s="11"/>
-      <c r="K76" s="11"/>
-      <c r="L76" s="11">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M76" s="11"/>
-      <c r="N76" s="11"/>
-      <c r="O76" s="11">
-        <v>0</v>
-      </c>
-      <c r="P76" s="11">
+      <c r="J76" s="10"/>
+      <c r="K76" s="10"/>
+      <c r="L76" s="10">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q76" s="13"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="10"/>
+      <c r="O76" s="10">
+        <v>0</v>
+      </c>
+      <c r="P76" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Q76" s="12"/>
       <c r="R76" s="4">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S76" s="8"/>
+      <c r="T76" s="8" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U76" s="10" t="e">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S76" s="19"/>
-      <c r="T76" s="8" t="e">
-        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U76" s="11" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V76" s="11">
-        <v>0</v>
-      </c>
-      <c r="W76" s="11">
-        <v>0</v>
-      </c>
-      <c r="X76" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y76" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z76" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA76" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB76" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC76" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD76" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE76" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF76" s="11" t="s">
+      <c r="V76" s="10">
+        <v>0</v>
+      </c>
+      <c r="W76" s="10">
+        <v>0</v>
+      </c>
+      <c r="X76" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="10" t="s">
         <v>86</v>
       </c>
       <c r="AG76" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH76" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH76" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AI76" s="8"/>
       <c r="AJ76" s="8"/>
       <c r="AK76" s="8"/>
@@ -14429,7 +14636,7 @@
         <v>225.41</v>
       </c>
       <c r="L77" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-0.98199999999999932</v>
       </c>
       <c r="M77" s="8"/>
@@ -14438,27 +14645,27 @@
         <v>73</v>
       </c>
       <c r="P77" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>44.885599999999997</v>
       </c>
       <c r="Q77" s="4">
-        <f t="shared" ref="Q77:Q78" si="28">11*P77-O77-F77</f>
+        <f t="shared" ref="Q77:Q78" si="30">11*P77-O77-F77</f>
         <v>350.54159999999996</v>
       </c>
       <c r="R77" s="4">
-        <f t="shared" ref="R77:R79" si="29">S77</f>
+        <f t="shared" ref="R77:R79" si="31">S77</f>
         <v>450</v>
       </c>
-      <c r="S77" s="19">
+      <c r="S77" s="8">
         <f>VLOOKUP(A77,[1]Sheet!$A:$R,18,0)</f>
         <v>450</v>
       </c>
       <c r="T77" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>13.215819772933861</v>
       </c>
       <c r="U77" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>3.1903327570534872</v>
       </c>
       <c r="V77" s="8">
@@ -14493,10 +14700,13 @@
       </c>
       <c r="AF77" s="8"/>
       <c r="AG77" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>450</v>
       </c>
-      <c r="AH77" s="8"/>
+      <c r="AH77" s="8">
+        <f t="shared" si="28"/>
+        <v>44.885599999999997</v>
+      </c>
       <c r="AI77" s="8"/>
       <c r="AJ77" s="8"/>
       <c r="AK77" s="8"/>
@@ -14547,7 +14757,7 @@
         <v>263.8</v>
       </c>
       <c r="L78" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>15.781000000000006</v>
       </c>
       <c r="M78" s="8"/>
@@ -14556,27 +14766,27 @@
         <v>22</v>
       </c>
       <c r="P78" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>55.916200000000003</v>
       </c>
       <c r="Q78" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>468.87320000000005</v>
       </c>
       <c r="R78" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>600</v>
       </c>
-      <c r="S78" s="19">
+      <c r="S78" s="8">
         <f>VLOOKUP(A78,[1]Sheet!$A:$R,18,0)</f>
         <v>600</v>
       </c>
       <c r="T78" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>13.345059213608934</v>
       </c>
       <c r="U78" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2.6147163076174702</v>
       </c>
       <c r="V78" s="8">
@@ -14611,10 +14821,13 @@
       </c>
       <c r="AF78" s="8"/>
       <c r="AG78" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>600</v>
       </c>
-      <c r="AH78" s="8"/>
+      <c r="AH78" s="8">
+        <f t="shared" si="28"/>
+        <v>55.916200000000003</v>
+      </c>
       <c r="AI78" s="8"/>
       <c r="AJ78" s="8"/>
       <c r="AK78" s="8"/>
@@ -14665,7 +14878,7 @@
         <v>404</v>
       </c>
       <c r="L79" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-13</v>
       </c>
       <c r="M79" s="8"/>
@@ -14674,27 +14887,27 @@
         <v>0</v>
       </c>
       <c r="P79" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>78.2</v>
       </c>
       <c r="Q79" s="4">
-        <f t="shared" ref="Q79:Q85" si="30">15*P79-O79-F79</f>
+        <f t="shared" ref="Q79:Q85" si="32">15*P79-O79-F79</f>
         <v>434</v>
       </c>
       <c r="R79" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>600</v>
       </c>
-      <c r="S79" s="19">
+      <c r="S79" s="8">
         <f>VLOOKUP(A79,[1]Sheet!$A:$R,18,0)</f>
         <v>600</v>
       </c>
       <c r="T79" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>17.122762148337596</v>
       </c>
       <c r="U79" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.4501278772378505</v>
       </c>
       <c r="V79" s="8">
@@ -14729,10 +14942,13 @@
       </c>
       <c r="AF79" s="8"/>
       <c r="AG79" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>210</v>
       </c>
-      <c r="AH79" s="8"/>
+      <c r="AH79" s="8">
+        <f t="shared" si="28"/>
+        <v>27.37</v>
+      </c>
       <c r="AI79" s="8"/>
       <c r="AJ79" s="8"/>
       <c r="AK79" s="8"/>
@@ -14783,7 +14999,7 @@
         <v>94</v>
       </c>
       <c r="L80" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-5</v>
       </c>
       <c r="M80" s="8"/>
@@ -14792,24 +15008,24 @@
         <v>86</v>
       </c>
       <c r="P80" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>17.8</v>
       </c>
       <c r="Q80" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>99</v>
       </c>
       <c r="R80" s="4">
+        <f t="shared" si="25"/>
+        <v>99</v>
+      </c>
+      <c r="S80" s="8"/>
+      <c r="T80" s="8">
+        <f t="shared" si="26"/>
+        <v>15</v>
+      </c>
+      <c r="U80" s="8">
         <f t="shared" si="24"/>
-        <v>99</v>
-      </c>
-      <c r="S80" s="19"/>
-      <c r="T80" s="8">
-        <f t="shared" si="25"/>
-        <v>15</v>
-      </c>
-      <c r="U80" s="8">
-        <f t="shared" si="23"/>
         <v>9.4382022471910112</v>
       </c>
       <c r="V80" s="8">
@@ -14844,10 +15060,13 @@
       </c>
       <c r="AF80" s="8"/>
       <c r="AG80" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>29.7</v>
       </c>
-      <c r="AH80" s="8"/>
+      <c r="AH80" s="8">
+        <f t="shared" si="28"/>
+        <v>5.34</v>
+      </c>
       <c r="AI80" s="8"/>
       <c r="AJ80" s="8"/>
       <c r="AK80" s="8"/>
@@ -14898,7 +15117,7 @@
         <v>70</v>
       </c>
       <c r="L81" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M81" s="8"/>
@@ -14907,24 +15126,24 @@
         <v>112</v>
       </c>
       <c r="P81" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>14</v>
       </c>
       <c r="Q81" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>90</v>
       </c>
       <c r="R81" s="4">
+        <f t="shared" si="25"/>
+        <v>90</v>
+      </c>
+      <c r="S81" s="8"/>
+      <c r="T81" s="8">
+        <f t="shared" si="26"/>
+        <v>15</v>
+      </c>
+      <c r="U81" s="8">
         <f t="shared" si="24"/>
-        <v>90</v>
-      </c>
-      <c r="S81" s="19"/>
-      <c r="T81" s="8">
-        <f t="shared" si="25"/>
-        <v>15</v>
-      </c>
-      <c r="U81" s="8">
-        <f t="shared" si="23"/>
         <v>8.5714285714285712</v>
       </c>
       <c r="V81" s="8">
@@ -14959,10 +15178,13 @@
       </c>
       <c r="AF81" s="8"/>
       <c r="AG81" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>27</v>
       </c>
-      <c r="AH81" s="8"/>
+      <c r="AH81" s="8">
+        <f t="shared" si="28"/>
+        <v>4.2</v>
+      </c>
       <c r="AI81" s="8"/>
       <c r="AJ81" s="8"/>
       <c r="AK81" s="8"/>
@@ -15013,7 +15235,7 @@
         <v>298</v>
       </c>
       <c r="L82" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-11</v>
       </c>
       <c r="M82" s="8"/>
@@ -15022,7 +15244,7 @@
         <v>0</v>
       </c>
       <c r="P82" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>57.4</v>
       </c>
       <c r="Q82" s="4">
@@ -15030,19 +15252,19 @@
         <v>442.6</v>
       </c>
       <c r="R82" s="4">
-        <f t="shared" ref="R82:R84" si="31">S82</f>
+        <f t="shared" ref="R82:R83" si="33">S82</f>
         <v>600</v>
       </c>
-      <c r="S82" s="19">
+      <c r="S82" s="8">
         <f>VLOOKUP(A82,[1]Sheet!$A:$R,18,0)</f>
         <v>600</v>
       </c>
       <c r="T82" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>16.742160278745644</v>
       </c>
       <c r="U82" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6.2891986062717775</v>
       </c>
       <c r="V82" s="8">
@@ -15077,10 +15299,13 @@
       </c>
       <c r="AF82" s="8"/>
       <c r="AG82" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>168.00000000000003</v>
       </c>
-      <c r="AH82" s="8"/>
+      <c r="AH82" s="8">
+        <f t="shared" si="28"/>
+        <v>16.072000000000003</v>
+      </c>
       <c r="AI82" s="8"/>
       <c r="AJ82" s="8"/>
       <c r="AK82" s="8"/>
@@ -15131,7 +15356,7 @@
         <v>258</v>
       </c>
       <c r="L83" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-7</v>
       </c>
       <c r="M83" s="8"/>
@@ -15140,27 +15365,27 @@
         <v>0</v>
       </c>
       <c r="P83" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>50.2</v>
       </c>
       <c r="Q83" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>184</v>
       </c>
       <c r="R83" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>250</v>
       </c>
-      <c r="S83" s="19">
+      <c r="S83" s="8">
         <f>VLOOKUP(A83,[1]Sheet!$A:$R,18,0)</f>
         <v>250</v>
       </c>
       <c r="T83" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>16.314741035856574</v>
       </c>
       <c r="U83" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>11.334661354581673</v>
       </c>
       <c r="V83" s="8">
@@ -15195,10 +15420,13 @@
       </c>
       <c r="AF83" s="8"/>
       <c r="AG83" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>70</v>
       </c>
-      <c r="AH83" s="8"/>
+      <c r="AH83" s="8">
+        <f t="shared" si="28"/>
+        <v>14.056000000000003</v>
+      </c>
       <c r="AI83" s="8"/>
       <c r="AJ83" s="8"/>
       <c r="AK83" s="8"/>
@@ -15249,7 +15477,7 @@
         <v>176</v>
       </c>
       <c r="L84" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-15</v>
       </c>
       <c r="M84" s="8"/>
@@ -15258,23 +15486,23 @@
         <v>0</v>
       </c>
       <c r="P84" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>32.200000000000003</v>
       </c>
       <c r="Q84" s="4"/>
       <c r="R84" s="4">
         <v>120</v>
       </c>
-      <c r="S84" s="19">
+      <c r="S84" s="8">
         <f>VLOOKUP(A84,[1]Sheet!$A:$R,18,0)</f>
         <v>150</v>
       </c>
       <c r="T84" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>20.12422360248447</v>
       </c>
       <c r="U84" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>16.397515527950308</v>
       </c>
       <c r="V84" s="8">
@@ -15309,10 +15537,13 @@
       </c>
       <c r="AF84" s="8"/>
       <c r="AG84" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>33.6</v>
       </c>
-      <c r="AH84" s="8"/>
+      <c r="AH84" s="8">
+        <f t="shared" si="28"/>
+        <v>9.0160000000000018</v>
+      </c>
       <c r="AI84" s="8"/>
       <c r="AJ84" s="8"/>
       <c r="AK84" s="8"/>
@@ -15363,7 +15594,7 @@
         <v>209</v>
       </c>
       <c r="L85" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-4</v>
       </c>
       <c r="M85" s="8"/>
@@ -15372,24 +15603,24 @@
         <v>0</v>
       </c>
       <c r="P85" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>41</v>
       </c>
       <c r="Q85" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>309</v>
       </c>
       <c r="R85" s="4">
+        <f t="shared" si="25"/>
+        <v>309</v>
+      </c>
+      <c r="S85" s="8"/>
+      <c r="T85" s="8">
+        <f t="shared" si="26"/>
+        <v>15</v>
+      </c>
+      <c r="U85" s="8">
         <f t="shared" si="24"/>
-        <v>309</v>
-      </c>
-      <c r="S85" s="19"/>
-      <c r="T85" s="8">
-        <f t="shared" si="25"/>
-        <v>15</v>
-      </c>
-      <c r="U85" s="8">
-        <f t="shared" si="23"/>
         <v>7.4634146341463419</v>
       </c>
       <c r="V85" s="8">
@@ -15424,10 +15655,13 @@
       </c>
       <c r="AF85" s="8"/>
       <c r="AG85" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>123.60000000000001</v>
       </c>
-      <c r="AH85" s="8"/>
+      <c r="AH85" s="8">
+        <f t="shared" si="28"/>
+        <v>16.400000000000002</v>
+      </c>
       <c r="AI85" s="8"/>
       <c r="AJ85" s="8"/>
       <c r="AK85" s="8"/>
@@ -15446,94 +15680,97 @@
       <c r="AX85" s="8"/>
     </row>
     <row r="86" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A86" s="11" t="s">
+      <c r="A86" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C86" s="11">
+      <c r="C86" s="10">
         <v>-6.327</v>
       </c>
-      <c r="D86" s="11">
+      <c r="D86" s="10">
         <v>23.606000000000002</v>
       </c>
-      <c r="E86" s="11"/>
-      <c r="F86" s="11"/>
-      <c r="G86" s="12">
-        <v>0</v>
-      </c>
-      <c r="H86" s="11">
+      <c r="E86" s="10"/>
+      <c r="F86" s="10"/>
+      <c r="G86" s="11">
+        <v>0</v>
+      </c>
+      <c r="H86" s="10">
         <v>50</v>
       </c>
-      <c r="I86" s="11" t="s">
+      <c r="I86" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J86" s="11"/>
-      <c r="K86" s="11"/>
-      <c r="L86" s="11">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M86" s="11"/>
-      <c r="N86" s="11"/>
-      <c r="O86" s="11">
-        <v>0</v>
-      </c>
-      <c r="P86" s="11">
+      <c r="J86" s="10"/>
+      <c r="K86" s="10"/>
+      <c r="L86" s="10">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q86" s="13"/>
+      <c r="M86" s="10"/>
+      <c r="N86" s="10"/>
+      <c r="O86" s="10">
+        <v>0</v>
+      </c>
+      <c r="P86" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Q86" s="12"/>
       <c r="R86" s="4">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S86" s="8"/>
+      <c r="T86" s="8" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U86" s="10" t="e">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S86" s="19"/>
-      <c r="T86" s="8" t="e">
-        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U86" s="11" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V86" s="11">
-        <v>0</v>
-      </c>
-      <c r="W86" s="11">
-        <v>0</v>
-      </c>
-      <c r="X86" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y86" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z86" s="11">
+      <c r="V86" s="10">
+        <v>0</v>
+      </c>
+      <c r="W86" s="10">
+        <v>0</v>
+      </c>
+      <c r="X86" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="10">
         <v>-0.13800000000000001</v>
       </c>
-      <c r="AA86" s="11">
+      <c r="AA86" s="10">
         <v>11.125999999999999</v>
       </c>
-      <c r="AB86" s="11">
+      <c r="AB86" s="10">
         <v>8.2726000000000006</v>
       </c>
-      <c r="AC86" s="11">
+      <c r="AC86" s="10">
         <v>12.144600000000001</v>
       </c>
-      <c r="AD86" s="11">
+      <c r="AD86" s="10">
         <v>10.204599999999999</v>
       </c>
-      <c r="AE86" s="11">
+      <c r="AE86" s="10">
         <v>5.8887999999999998</v>
       </c>
-      <c r="AF86" s="11"/>
+      <c r="AF86" s="10"/>
       <c r="AG86" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH86" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH86" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AI86" s="8"/>
       <c r="AJ86" s="8"/>
       <c r="AK86" s="8"/>
@@ -15552,94 +15789,97 @@
       <c r="AX86" s="8"/>
     </row>
     <row r="87" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A87" s="11" t="s">
+      <c r="A87" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C87" s="11">
+      <c r="C87" s="10">
         <v>-2</v>
       </c>
-      <c r="D87" s="11">
+      <c r="D87" s="10">
         <v>2</v>
       </c>
-      <c r="E87" s="11"/>
-      <c r="F87" s="11"/>
-      <c r="G87" s="12">
-        <v>0</v>
-      </c>
-      <c r="H87" s="11">
+      <c r="E87" s="10"/>
+      <c r="F87" s="10"/>
+      <c r="G87" s="11">
+        <v>0</v>
+      </c>
+      <c r="H87" s="10">
         <v>50</v>
       </c>
-      <c r="I87" s="11" t="s">
+      <c r="I87" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J87" s="11"/>
-      <c r="K87" s="11"/>
-      <c r="L87" s="11">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M87" s="11"/>
-      <c r="N87" s="11"/>
-      <c r="O87" s="11">
-        <v>0</v>
-      </c>
-      <c r="P87" s="11">
+      <c r="J87" s="10"/>
+      <c r="K87" s="10"/>
+      <c r="L87" s="10">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q87" s="13"/>
+      <c r="M87" s="10"/>
+      <c r="N87" s="10"/>
+      <c r="O87" s="10">
+        <v>0</v>
+      </c>
+      <c r="P87" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Q87" s="12"/>
       <c r="R87" s="4">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S87" s="8"/>
+      <c r="T87" s="8" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U87" s="10" t="e">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S87" s="19"/>
-      <c r="T87" s="8" t="e">
-        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U87" s="11" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V87" s="11">
-        <v>0</v>
-      </c>
-      <c r="W87" s="11">
-        <v>0</v>
-      </c>
-      <c r="X87" s="11">
+      <c r="V87" s="10">
+        <v>0</v>
+      </c>
+      <c r="W87" s="10">
+        <v>0</v>
+      </c>
+      <c r="X87" s="10">
         <v>-0.4</v>
       </c>
-      <c r="Y87" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z87" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA87" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB87" s="11">
+      <c r="Y87" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="10">
         <v>5</v>
       </c>
-      <c r="AC87" s="11">
+      <c r="AC87" s="10">
         <v>8.6</v>
       </c>
-      <c r="AD87" s="11">
+      <c r="AD87" s="10">
         <v>3.2</v>
       </c>
-      <c r="AE87" s="11">
+      <c r="AE87" s="10">
         <v>5.4</v>
       </c>
-      <c r="AF87" s="11"/>
+      <c r="AF87" s="10"/>
       <c r="AG87" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH87" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH87" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AI87" s="8"/>
       <c r="AJ87" s="8"/>
       <c r="AK87" s="8"/>
@@ -15658,98 +15898,101 @@
       <c r="AX87" s="8"/>
     </row>
     <row r="88" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A88" s="11" t="s">
+      <c r="A88" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B88" s="11" t="s">
+      <c r="B88" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C88" s="11">
+      <c r="C88" s="10">
         <v>-5</v>
       </c>
-      <c r="D88" s="11">
+      <c r="D88" s="10">
         <v>14</v>
       </c>
-      <c r="E88" s="11"/>
-      <c r="F88" s="11"/>
-      <c r="G88" s="12">
-        <v>0</v>
-      </c>
-      <c r="H88" s="11">
+      <c r="E88" s="10"/>
+      <c r="F88" s="10"/>
+      <c r="G88" s="11">
+        <v>0</v>
+      </c>
+      <c r="H88" s="10">
         <v>60</v>
       </c>
-      <c r="I88" s="11" t="s">
+      <c r="I88" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J88" s="11" t="s">
+      <c r="J88" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="K88" s="11"/>
-      <c r="L88" s="11">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M88" s="11"/>
-      <c r="N88" s="11"/>
-      <c r="O88" s="11">
-        <v>0</v>
-      </c>
-      <c r="P88" s="11">
+      <c r="K88" s="10"/>
+      <c r="L88" s="10">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q88" s="13"/>
+      <c r="M88" s="10"/>
+      <c r="N88" s="10"/>
+      <c r="O88" s="10">
+        <v>0</v>
+      </c>
+      <c r="P88" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Q88" s="12"/>
       <c r="R88" s="4">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S88" s="8"/>
+      <c r="T88" s="8" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U88" s="10" t="e">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S88" s="19"/>
-      <c r="T88" s="8" t="e">
-        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U88" s="11" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V88" s="11">
+      <c r="V88" s="10">
         <v>-0.2</v>
       </c>
-      <c r="W88" s="11">
-        <v>0</v>
-      </c>
-      <c r="X88" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y88" s="11">
+      <c r="W88" s="10">
+        <v>0</v>
+      </c>
+      <c r="X88" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="10">
         <v>0.6</v>
       </c>
-      <c r="Z88" s="11">
+      <c r="Z88" s="10">
         <v>2.2000000000000002</v>
       </c>
-      <c r="AA88" s="11">
+      <c r="AA88" s="10">
         <v>5</v>
       </c>
-      <c r="AB88" s="11">
+      <c r="AB88" s="10">
         <v>5.6</v>
       </c>
-      <c r="AC88" s="11">
+      <c r="AC88" s="10">
         <v>7.2</v>
       </c>
-      <c r="AD88" s="11">
+      <c r="AD88" s="10">
         <v>6.4</v>
       </c>
-      <c r="AE88" s="11">
+      <c r="AE88" s="10">
         <v>9.1999999999999993</v>
       </c>
-      <c r="AF88" s="11" t="s">
+      <c r="AF88" s="10" t="s">
         <v>134</v>
       </c>
       <c r="AG88" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH88" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH88" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AI88" s="8"/>
       <c r="AJ88" s="8"/>
       <c r="AK88" s="8"/>
@@ -15768,98 +16011,101 @@
       <c r="AX88" s="8"/>
     </row>
     <row r="89" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A89" s="11" t="s">
+      <c r="A89" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C89" s="11">
+      <c r="C89" s="10">
         <v>0.30099999999999999</v>
       </c>
-      <c r="D89" s="11"/>
-      <c r="E89" s="11">
+      <c r="D89" s="10"/>
+      <c r="E89" s="10">
         <v>-0.30599999999999999</v>
       </c>
-      <c r="F89" s="11"/>
-      <c r="G89" s="12">
+      <c r="F89" s="10"/>
+      <c r="G89" s="11">
         <v>1</v>
       </c>
-      <c r="H89" s="11">
+      <c r="H89" s="10">
         <v>30</v>
       </c>
-      <c r="I89" s="11" t="s">
+      <c r="I89" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J89" s="11"/>
-      <c r="K89" s="11"/>
-      <c r="L89" s="11">
-        <f t="shared" si="21"/>
+      <c r="J89" s="10"/>
+      <c r="K89" s="10"/>
+      <c r="L89" s="10">
+        <f t="shared" si="22"/>
         <v>-0.30599999999999999</v>
       </c>
-      <c r="M89" s="11"/>
-      <c r="N89" s="11"/>
-      <c r="O89" s="11">
-        <v>0</v>
-      </c>
-      <c r="P89" s="11">
-        <f t="shared" si="22"/>
+      <c r="M89" s="10"/>
+      <c r="N89" s="10"/>
+      <c r="O89" s="10">
+        <v>0</v>
+      </c>
+      <c r="P89" s="10">
+        <f t="shared" si="23"/>
         <v>-6.1199999999999997E-2</v>
       </c>
-      <c r="Q89" s="13"/>
+      <c r="Q89" s="12"/>
       <c r="R89" s="4">
         <v>100</v>
       </c>
-      <c r="S89" s="19">
+      <c r="S89" s="8">
         <f>VLOOKUP(A89,[1]Sheet!$A:$R,18,0)</f>
         <v>300</v>
       </c>
       <c r="T89" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-1633.9869281045753</v>
       </c>
-      <c r="U89" s="11">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="V89" s="11">
-        <v>0</v>
-      </c>
-      <c r="W89" s="11">
-        <v>0</v>
-      </c>
-      <c r="X89" s="11">
+      <c r="U89" s="10">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="V89" s="10">
+        <v>0</v>
+      </c>
+      <c r="W89" s="10">
+        <v>0</v>
+      </c>
+      <c r="X89" s="10">
         <v>-0.16059999999999999</v>
       </c>
-      <c r="Y89" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA89" s="11">
+      <c r="Y89" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="10">
         <v>7.1199999999999999E-2</v>
       </c>
-      <c r="AB89" s="11">
+      <c r="AB89" s="10">
         <v>0.36159999999999998</v>
       </c>
-      <c r="AC89" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD89" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE89" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF89" s="14" t="s">
+      <c r="AC89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="13" t="s">
         <v>179</v>
       </c>
       <c r="AG89" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>100</v>
       </c>
-      <c r="AH89" s="8"/>
+      <c r="AH89" s="8">
+        <f t="shared" si="28"/>
+        <v>-6.1199999999999997E-2</v>
+      </c>
       <c r="AI89" s="8"/>
       <c r="AJ89" s="8"/>
       <c r="AK89" s="8"/>
@@ -15878,98 +16124,101 @@
       <c r="AX89" s="8"/>
     </row>
     <row r="90" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A90" s="11" t="s">
+      <c r="A90" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B90" s="11" t="s">
+      <c r="B90" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C90" s="11">
+      <c r="C90" s="10">
         <v>146</v>
       </c>
-      <c r="D90" s="11">
+      <c r="D90" s="10">
         <v>90</v>
       </c>
-      <c r="E90" s="11">
+      <c r="E90" s="10">
         <v>139</v>
       </c>
-      <c r="F90" s="11"/>
-      <c r="G90" s="12">
-        <v>0</v>
-      </c>
-      <c r="H90" s="11">
+      <c r="F90" s="10"/>
+      <c r="G90" s="11">
+        <v>0</v>
+      </c>
+      <c r="H90" s="10">
         <v>50</v>
       </c>
-      <c r="I90" s="11" t="s">
+      <c r="I90" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="J90" s="11"/>
-      <c r="K90" s="11">
+      <c r="J90" s="10"/>
+      <c r="K90" s="10">
         <v>141</v>
       </c>
-      <c r="L90" s="11">
-        <f t="shared" si="21"/>
+      <c r="L90" s="10">
+        <f t="shared" si="22"/>
         <v>-2</v>
       </c>
-      <c r="M90" s="11"/>
-      <c r="N90" s="11"/>
-      <c r="O90" s="11">
-        <v>0</v>
-      </c>
-      <c r="P90" s="11">
-        <f t="shared" si="22"/>
+      <c r="M90" s="10"/>
+      <c r="N90" s="10"/>
+      <c r="O90" s="10">
+        <v>0</v>
+      </c>
+      <c r="P90" s="10">
+        <f t="shared" si="23"/>
         <v>27.8</v>
       </c>
-      <c r="Q90" s="13"/>
+      <c r="Q90" s="12"/>
       <c r="R90" s="4">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S90" s="8"/>
+      <c r="T90" s="8">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="U90" s="10">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S90" s="19"/>
-      <c r="T90" s="8">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="U90" s="11">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="V90" s="11">
+      <c r="V90" s="10">
         <v>27.4</v>
       </c>
-      <c r="W90" s="11">
+      <c r="W90" s="10">
         <v>19.2</v>
       </c>
-      <c r="X90" s="11">
+      <c r="X90" s="10">
         <v>10</v>
       </c>
-      <c r="Y90" s="11">
+      <c r="Y90" s="10">
         <v>35.6</v>
       </c>
-      <c r="Z90" s="11">
+      <c r="Z90" s="10">
         <v>21.6</v>
       </c>
-      <c r="AA90" s="11">
+      <c r="AA90" s="10">
         <v>6.6</v>
       </c>
-      <c r="AB90" s="11">
+      <c r="AB90" s="10">
         <v>19</v>
       </c>
-      <c r="AC90" s="11">
+      <c r="AC90" s="10">
         <v>32.4</v>
       </c>
-      <c r="AD90" s="11">
+      <c r="AD90" s="10">
         <v>15.4</v>
       </c>
-      <c r="AE90" s="11">
+      <c r="AE90" s="10">
         <v>20.6</v>
       </c>
-      <c r="AF90" s="11"/>
+      <c r="AF90" s="10"/>
       <c r="AG90" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH90" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH90" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AI90" s="8"/>
       <c r="AJ90" s="8"/>
       <c r="AK90" s="8"/>
@@ -15988,96 +16237,99 @@
       <c r="AX90" s="8"/>
     </row>
     <row r="91" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A91" s="11" t="s">
+      <c r="A91" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B91" s="11" t="s">
+      <c r="B91" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C91" s="11">
+      <c r="C91" s="10">
         <v>12</v>
       </c>
-      <c r="D91" s="11">
+      <c r="D91" s="10">
         <v>28</v>
       </c>
-      <c r="E91" s="11"/>
-      <c r="F91" s="11"/>
-      <c r="G91" s="12">
-        <v>0</v>
-      </c>
-      <c r="H91" s="11">
+      <c r="E91" s="10"/>
+      <c r="F91" s="10"/>
+      <c r="G91" s="11">
+        <v>0</v>
+      </c>
+      <c r="H91" s="10">
         <v>50</v>
       </c>
-      <c r="I91" s="11" t="s">
+      <c r="I91" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J91" s="11"/>
-      <c r="K91" s="11">
+      <c r="J91" s="10"/>
+      <c r="K91" s="10">
         <v>31</v>
       </c>
-      <c r="L91" s="11">
-        <f t="shared" si="21"/>
+      <c r="L91" s="10">
+        <f t="shared" si="22"/>
         <v>-31</v>
       </c>
-      <c r="M91" s="11"/>
-      <c r="N91" s="11"/>
-      <c r="O91" s="11">
-        <v>0</v>
-      </c>
-      <c r="P91" s="11">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="Q91" s="13"/>
+      <c r="M91" s="10"/>
+      <c r="N91" s="10"/>
+      <c r="O91" s="10">
+        <v>0</v>
+      </c>
+      <c r="P91" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Q91" s="12"/>
       <c r="R91" s="4">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S91" s="8"/>
+      <c r="T91" s="8" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U91" s="10" t="e">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S91" s="19"/>
-      <c r="T91" s="8" t="e">
-        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U91" s="11" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V91" s="11">
-        <v>0</v>
-      </c>
-      <c r="W91" s="11">
-        <v>0</v>
-      </c>
-      <c r="X91" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="11">
+      <c r="V91" s="10">
+        <v>0</v>
+      </c>
+      <c r="W91" s="10">
+        <v>0</v>
+      </c>
+      <c r="X91" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="10">
         <v>0.4</v>
       </c>
-      <c r="Z91" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="11">
+      <c r="Z91" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="10">
         <v>12.6</v>
       </c>
-      <c r="AC91" s="11">
+      <c r="AC91" s="10">
         <v>8.8000000000000007</v>
       </c>
-      <c r="AD91" s="11">
+      <c r="AD91" s="10">
         <v>8</v>
       </c>
-      <c r="AE91" s="11">
+      <c r="AE91" s="10">
         <v>11</v>
       </c>
-      <c r="AF91" s="11"/>
+      <c r="AF91" s="10"/>
       <c r="AG91" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH91" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH91" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AI91" s="8"/>
       <c r="AJ91" s="8"/>
       <c r="AK91" s="8"/>
@@ -16096,98 +16348,101 @@
       <c r="AX91" s="8"/>
     </row>
     <row r="92" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A92" s="11" t="s">
+      <c r="A92" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C92" s="11">
+      <c r="C92" s="10">
         <v>1</v>
       </c>
-      <c r="D92" s="11">
+      <c r="D92" s="10">
         <v>5</v>
       </c>
-      <c r="E92" s="11">
+      <c r="E92" s="10">
         <v>-1</v>
       </c>
-      <c r="F92" s="11"/>
-      <c r="G92" s="12">
-        <v>0</v>
-      </c>
-      <c r="H92" s="11">
+      <c r="F92" s="10"/>
+      <c r="G92" s="11">
+        <v>0</v>
+      </c>
+      <c r="H92" s="10">
         <v>60</v>
       </c>
-      <c r="I92" s="11" t="s">
+      <c r="I92" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J92" s="11"/>
-      <c r="K92" s="11">
+      <c r="J92" s="10"/>
+      <c r="K92" s="10">
         <v>38</v>
       </c>
-      <c r="L92" s="11">
-        <f t="shared" si="21"/>
+      <c r="L92" s="10">
+        <f t="shared" si="22"/>
         <v>-39</v>
       </c>
-      <c r="M92" s="11"/>
-      <c r="N92" s="11"/>
-      <c r="O92" s="11">
-        <v>0</v>
-      </c>
-      <c r="P92" s="11">
-        <f t="shared" si="22"/>
+      <c r="M92" s="10"/>
+      <c r="N92" s="10"/>
+      <c r="O92" s="10">
+        <v>0</v>
+      </c>
+      <c r="P92" s="10">
+        <f t="shared" si="23"/>
         <v>-0.2</v>
       </c>
-      <c r="Q92" s="13"/>
+      <c r="Q92" s="12"/>
       <c r="R92" s="4">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S92" s="8"/>
+      <c r="T92" s="8">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="U92" s="10">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S92" s="19"/>
-      <c r="T92" s="8">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="U92" s="11">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="V92" s="11">
-        <v>0</v>
-      </c>
-      <c r="W92" s="11">
+      <c r="V92" s="10">
+        <v>0</v>
+      </c>
+      <c r="W92" s="10">
         <v>1.4</v>
       </c>
-      <c r="X92" s="11">
+      <c r="X92" s="10">
         <v>1.8</v>
       </c>
-      <c r="Y92" s="11">
+      <c r="Y92" s="10">
         <v>0.4</v>
       </c>
-      <c r="Z92" s="11">
+      <c r="Z92" s="10">
         <v>3.8</v>
       </c>
-      <c r="AA92" s="11">
+      <c r="AA92" s="10">
         <v>6.6</v>
       </c>
-      <c r="AB92" s="11">
+      <c r="AB92" s="10">
         <v>2.2000000000000002</v>
       </c>
-      <c r="AC92" s="11">
+      <c r="AC92" s="10">
         <v>2.8</v>
       </c>
-      <c r="AD92" s="11">
+      <c r="AD92" s="10">
         <v>3.6</v>
       </c>
-      <c r="AE92" s="11">
+      <c r="AE92" s="10">
         <v>8</v>
       </c>
-      <c r="AF92" s="11"/>
+      <c r="AF92" s="10"/>
       <c r="AG92" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH92" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH92" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AI92" s="8"/>
       <c r="AJ92" s="8"/>
       <c r="AK92" s="8"/>
@@ -16236,7 +16491,7 @@
         <v>24</v>
       </c>
       <c r="L93" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2</v>
       </c>
       <c r="M93" s="8"/>
@@ -16245,24 +16500,24 @@
         <v>0</v>
       </c>
       <c r="P93" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5.2</v>
       </c>
       <c r="Q93" s="4"/>
       <c r="R93" s="4">
-        <f t="shared" ref="R93:R94" si="32">S93</f>
+        <f t="shared" ref="R93:R94" si="34">S93</f>
         <v>150</v>
       </c>
-      <c r="S93" s="19">
+      <c r="S93" s="8">
         <f>VLOOKUP(A93,[1]Sheet!$A:$R,18,0)</f>
         <v>150</v>
       </c>
       <c r="T93" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>51.53846153846154</v>
       </c>
       <c r="U93" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>22.69230769230769</v>
       </c>
       <c r="V93" s="8">
@@ -16299,10 +16554,13 @@
         <v>37</v>
       </c>
       <c r="AG93" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>50.7</v>
       </c>
-      <c r="AH93" s="8"/>
+      <c r="AH93" s="8">
+        <f t="shared" si="28"/>
+        <v>1.7576000000000003</v>
+      </c>
       <c r="AI93" s="8"/>
       <c r="AJ93" s="8"/>
       <c r="AK93" s="8"/>
@@ -16351,7 +16609,7 @@
         <v>24</v>
       </c>
       <c r="L94" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M94" s="8"/>
@@ -16360,24 +16618,24 @@
         <v>0</v>
       </c>
       <c r="P94" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>4.8</v>
       </c>
       <c r="Q94" s="4"/>
       <c r="R94" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>150</v>
       </c>
-      <c r="S94" s="19">
+      <c r="S94" s="8">
         <f>VLOOKUP(A94,[1]Sheet!$A:$R,18,0)</f>
         <v>150</v>
       </c>
       <c r="T94" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>56.25</v>
       </c>
       <c r="U94" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>25</v>
       </c>
       <c r="V94" s="8">
@@ -16414,10 +16672,13 @@
         <v>37</v>
       </c>
       <c r="AG94" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>48.75</v>
       </c>
-      <c r="AH94" s="8"/>
+      <c r="AH94" s="8">
+        <f t="shared" si="28"/>
+        <v>1.56</v>
+      </c>
       <c r="AI94" s="8"/>
       <c r="AJ94" s="8"/>
       <c r="AK94" s="8"/>
@@ -16468,7 +16729,7 @@
         <v>150</v>
       </c>
       <c r="L95" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-13</v>
       </c>
       <c r="M95" s="8"/>
@@ -16477,21 +16738,21 @@
         <v>0</v>
       </c>
       <c r="P95" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>27.4</v>
       </c>
       <c r="Q95" s="4"/>
       <c r="R95" s="4">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S95" s="8"/>
+      <c r="T95" s="8">
+        <f t="shared" si="26"/>
+        <v>15.547445255474454</v>
+      </c>
+      <c r="U95" s="8">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S95" s="19"/>
-      <c r="T95" s="8">
-        <f t="shared" si="25"/>
-        <v>15.547445255474454</v>
-      </c>
-      <c r="U95" s="8">
-        <f t="shared" si="23"/>
         <v>15.547445255474454</v>
       </c>
       <c r="V95" s="8">
@@ -16524,14 +16785,17 @@
       <c r="AE95" s="8">
         <v>49.6</v>
       </c>
-      <c r="AF95" s="16" t="s">
+      <c r="AF95" s="15" t="s">
         <v>40</v>
       </c>
       <c r="AG95" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH95" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH95" s="8">
+        <f t="shared" si="28"/>
+        <v>3.2879999999999998</v>
+      </c>
       <c r="AI95" s="8"/>
       <c r="AJ95" s="8"/>
       <c r="AK95" s="8"/>
@@ -16580,7 +16844,7 @@
         <v>14</v>
       </c>
       <c r="L96" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M96" s="8"/>
@@ -16589,24 +16853,24 @@
         <v>0</v>
       </c>
       <c r="P96" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2.8</v>
       </c>
       <c r="Q96" s="4"/>
       <c r="R96" s="4">
-        <f t="shared" ref="R96:R97" si="33">S96</f>
+        <f t="shared" ref="R96:R97" si="35">S96</f>
         <v>250</v>
       </c>
-      <c r="S96" s="19">
+      <c r="S96" s="8">
         <f>VLOOKUP(A96,[1]Sheet!$A:$R,18,0)</f>
         <v>250</v>
       </c>
       <c r="T96" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>118.57142857142858</v>
       </c>
       <c r="U96" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>29.285714285714288</v>
       </c>
       <c r="V96" s="8">
@@ -16643,10 +16907,13 @@
         <v>37</v>
       </c>
       <c r="AG96" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>37.5</v>
       </c>
-      <c r="AH96" s="8"/>
+      <c r="AH96" s="8">
+        <f t="shared" si="28"/>
+        <v>0.42</v>
+      </c>
       <c r="AI96" s="8"/>
       <c r="AJ96" s="8"/>
       <c r="AK96" s="8"/>
@@ -16695,7 +16962,7 @@
         <v>13</v>
       </c>
       <c r="L97" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M97" s="8"/>
@@ -16704,24 +16971,24 @@
         <v>0</v>
       </c>
       <c r="P97" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2.6</v>
       </c>
       <c r="Q97" s="4"/>
       <c r="R97" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>250</v>
       </c>
-      <c r="S97" s="19">
+      <c r="S97" s="8">
         <f>VLOOKUP(A97,[1]Sheet!$A:$R,18,0)</f>
         <v>250</v>
       </c>
       <c r="T97" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>122.69230769230769</v>
       </c>
       <c r="U97" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>26.538461538461537</v>
       </c>
       <c r="V97" s="8">
@@ -16758,10 +17025,13 @@
         <v>37</v>
       </c>
       <c r="AG97" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>37.5</v>
       </c>
-      <c r="AH97" s="8"/>
+      <c r="AH97" s="8">
+        <f t="shared" si="28"/>
+        <v>0.39</v>
+      </c>
       <c r="AI97" s="8"/>
       <c r="AJ97" s="8"/>
       <c r="AK97" s="8"/>
@@ -16812,7 +17082,7 @@
         <v>36</v>
       </c>
       <c r="L98" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-13</v>
       </c>
       <c r="M98" s="8"/>
@@ -16821,21 +17091,21 @@
         <v>74</v>
       </c>
       <c r="P98" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="Q98" s="4"/>
       <c r="R98" s="4">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S98" s="8"/>
+      <c r="T98" s="8">
+        <f t="shared" si="26"/>
+        <v>25.65217391304348</v>
+      </c>
+      <c r="U98" s="8">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S98" s="19"/>
-      <c r="T98" s="8">
-        <f t="shared" si="25"/>
-        <v>25.65217391304348</v>
-      </c>
-      <c r="U98" s="8">
-        <f t="shared" si="23"/>
         <v>25.65217391304348</v>
       </c>
       <c r="V98" s="8">
@@ -16872,10 +17142,13 @@
         <v>146</v>
       </c>
       <c r="AG98" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH98" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH98" s="8">
+        <f t="shared" si="28"/>
+        <v>1.518</v>
+      </c>
       <c r="AI98" s="8"/>
       <c r="AJ98" s="8"/>
       <c r="AK98" s="8"/>
@@ -16924,7 +17197,7 @@
         <v>7</v>
       </c>
       <c r="L99" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M99" s="8"/>
@@ -16933,7 +17206,7 @@
         <v>0</v>
       </c>
       <c r="P99" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1.4</v>
       </c>
       <c r="Q99" s="4"/>
@@ -16941,16 +17214,16 @@
         <f>S99</f>
         <v>250</v>
       </c>
-      <c r="S99" s="19">
+      <c r="S99" s="8">
         <f>VLOOKUP(A99,[1]Sheet!$A:$R,18,0)</f>
         <v>250</v>
       </c>
       <c r="T99" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>237.85714285714286</v>
       </c>
       <c r="U99" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>59.285714285714292</v>
       </c>
       <c r="V99" s="8">
@@ -16987,10 +17260,13 @@
         <v>148</v>
       </c>
       <c r="AG99" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>37.5</v>
       </c>
-      <c r="AH99" s="8"/>
+      <c r="AH99" s="8">
+        <f t="shared" si="28"/>
+        <v>0.21</v>
+      </c>
       <c r="AI99" s="8"/>
       <c r="AJ99" s="8"/>
       <c r="AK99" s="8"/>
@@ -17009,98 +17285,101 @@
       <c r="AX99" s="8"/>
     </row>
     <row r="100" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A100" s="11" t="s">
+      <c r="A100" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="B100" s="11" t="s">
+      <c r="B100" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C100" s="11">
+      <c r="C100" s="10">
         <v>-7</v>
       </c>
-      <c r="D100" s="11">
+      <c r="D100" s="10">
         <v>7</v>
       </c>
-      <c r="E100" s="11">
+      <c r="E100" s="10">
         <v>-1</v>
       </c>
-      <c r="F100" s="11"/>
-      <c r="G100" s="12">
-        <v>0</v>
-      </c>
-      <c r="H100" s="11">
+      <c r="F100" s="10"/>
+      <c r="G100" s="11">
+        <v>0</v>
+      </c>
+      <c r="H100" s="10">
         <v>45</v>
       </c>
-      <c r="I100" s="11" t="s">
+      <c r="I100" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="J100" s="11"/>
-      <c r="K100" s="11"/>
-      <c r="L100" s="11">
-        <f t="shared" si="21"/>
+      <c r="J100" s="10"/>
+      <c r="K100" s="10"/>
+      <c r="L100" s="10">
+        <f t="shared" si="22"/>
         <v>-1</v>
       </c>
-      <c r="M100" s="11"/>
-      <c r="N100" s="11"/>
-      <c r="O100" s="11">
-        <v>0</v>
-      </c>
-      <c r="P100" s="11">
-        <f t="shared" si="22"/>
+      <c r="M100" s="10"/>
+      <c r="N100" s="10"/>
+      <c r="O100" s="10">
+        <v>0</v>
+      </c>
+      <c r="P100" s="10">
+        <f t="shared" si="23"/>
         <v>-0.2</v>
       </c>
-      <c r="Q100" s="13"/>
+      <c r="Q100" s="12"/>
       <c r="R100" s="4">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S100" s="8"/>
+      <c r="T100" s="8">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="U100" s="10">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S100" s="19"/>
-      <c r="T100" s="8">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="U100" s="11">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="V100" s="11">
-        <v>0</v>
-      </c>
-      <c r="W100" s="11">
-        <v>0</v>
-      </c>
-      <c r="X100" s="11">
+      <c r="V100" s="10">
+        <v>0</v>
+      </c>
+      <c r="W100" s="10">
+        <v>0</v>
+      </c>
+      <c r="X100" s="10">
         <v>-0.6</v>
       </c>
-      <c r="Y100" s="11">
+      <c r="Y100" s="10">
         <v>-1</v>
       </c>
-      <c r="Z100" s="11">
+      <c r="Z100" s="10">
         <v>2.4</v>
       </c>
-      <c r="AA100" s="11">
+      <c r="AA100" s="10">
         <v>8.4</v>
       </c>
-      <c r="AB100" s="11">
+      <c r="AB100" s="10">
         <v>8.1999999999999993</v>
       </c>
-      <c r="AC100" s="11">
+      <c r="AC100" s="10">
         <v>3.2</v>
       </c>
-      <c r="AD100" s="11">
+      <c r="AD100" s="10">
         <v>1.8</v>
       </c>
-      <c r="AE100" s="11">
+      <c r="AE100" s="10">
         <v>4</v>
       </c>
-      <c r="AF100" s="11" t="s">
+      <c r="AF100" s="10" t="s">
         <v>72</v>
       </c>
       <c r="AG100" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH100" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH100" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AI100" s="8"/>
       <c r="AJ100" s="8"/>
       <c r="AK100" s="8"/>
@@ -17149,7 +17428,7 @@
         <v>10</v>
       </c>
       <c r="L101" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M101" s="8"/>
@@ -17158,24 +17437,24 @@
         <v>0</v>
       </c>
       <c r="P101" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2</v>
       </c>
       <c r="Q101" s="4"/>
       <c r="R101" s="4">
-        <f t="shared" ref="R101:R104" si="34">S101</f>
+        <f t="shared" ref="R101:R104" si="36">S101</f>
         <v>70</v>
       </c>
-      <c r="S101" s="19">
+      <c r="S101" s="8">
         <f>VLOOKUP(A101,[1]Sheet!$A:$R,18,0)</f>
         <v>70</v>
       </c>
       <c r="T101" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>74</v>
       </c>
       <c r="U101" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>39</v>
       </c>
       <c r="V101" s="8">
@@ -17212,10 +17491,13 @@
         <v>148</v>
       </c>
       <c r="AG101" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>18.2</v>
       </c>
-      <c r="AH101" s="8"/>
+      <c r="AH101" s="8">
+        <f t="shared" si="28"/>
+        <v>0.52</v>
+      </c>
       <c r="AI101" s="8"/>
       <c r="AJ101" s="8"/>
       <c r="AK101" s="8"/>
@@ -17264,7 +17546,7 @@
         <v>7</v>
       </c>
       <c r="L102" s="8">
-        <f t="shared" ref="L102:L119" si="35">E102-K102</f>
+        <f t="shared" ref="L102:L119" si="37">E102-K102</f>
         <v>1.2409999999999997</v>
       </c>
       <c r="M102" s="8"/>
@@ -17273,24 +17555,24 @@
         <v>0</v>
       </c>
       <c r="P102" s="8">
-        <f t="shared" ref="P102:P119" si="36">E102/5</f>
+        <f t="shared" ref="P102:P119" si="38">E102/5</f>
         <v>1.6481999999999999</v>
       </c>
       <c r="Q102" s="4"/>
       <c r="R102" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>50</v>
       </c>
-      <c r="S102" s="19">
+      <c r="S102" s="8">
         <f>VLOOKUP(A102,[1]Sheet!$A:$R,18,0)</f>
         <v>50</v>
       </c>
       <c r="T102" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>84.910811794685117</v>
       </c>
       <c r="U102" s="8">
-        <f t="shared" ref="U102:U119" si="37">(F102+O102)/P102</f>
+        <f t="shared" ref="U102:U119" si="39">(F102+O102)/P102</f>
         <v>54.574687537920163</v>
       </c>
       <c r="V102" s="8">
@@ -17327,10 +17609,13 @@
         <v>37</v>
       </c>
       <c r="AG102" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>50</v>
       </c>
-      <c r="AH102" s="8"/>
+      <c r="AH102" s="8">
+        <f t="shared" si="28"/>
+        <v>1.6481999999999999</v>
+      </c>
       <c r="AI102" s="8"/>
       <c r="AJ102" s="8"/>
       <c r="AK102" s="8"/>
@@ -17379,7 +17664,7 @@
         <v>6</v>
       </c>
       <c r="L103" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="M103" s="8"/>
@@ -17388,24 +17673,24 @@
         <v>0</v>
       </c>
       <c r="P103" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>1.2</v>
       </c>
       <c r="Q103" s="4"/>
       <c r="R103" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>70</v>
       </c>
-      <c r="S103" s="19">
+      <c r="S103" s="8">
         <f>VLOOKUP(A103,[1]Sheet!$A:$R,18,0)</f>
         <v>70</v>
       </c>
       <c r="T103" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>133.33333333333334</v>
       </c>
       <c r="U103" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>75</v>
       </c>
       <c r="V103" s="8">
@@ -17442,10 +17727,13 @@
         <v>148</v>
       </c>
       <c r="AG103" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>21.7</v>
       </c>
-      <c r="AH103" s="8"/>
+      <c r="AH103" s="8">
+        <f t="shared" si="28"/>
+        <v>0.372</v>
+      </c>
       <c r="AI103" s="8"/>
       <c r="AJ103" s="8"/>
       <c r="AK103" s="8"/>
@@ -17494,7 +17782,7 @@
         <v>7.6</v>
       </c>
       <c r="L104" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-2.8949999999999996</v>
       </c>
       <c r="M104" s="8"/>
@@ -17503,24 +17791,24 @@
         <v>0</v>
       </c>
       <c r="P104" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.94100000000000006</v>
       </c>
       <c r="Q104" s="4"/>
       <c r="R104" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>50</v>
       </c>
-      <c r="S104" s="19">
+      <c r="S104" s="8">
         <f>VLOOKUP(A104,[1]Sheet!$A:$R,18,0)</f>
         <v>50</v>
       </c>
       <c r="T104" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>156.7481402763018</v>
       </c>
       <c r="U104" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>103.61317747077577</v>
       </c>
       <c r="V104" s="8">
@@ -17557,10 +17845,13 @@
         <v>37</v>
       </c>
       <c r="AG104" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>50</v>
       </c>
-      <c r="AH104" s="8"/>
+      <c r="AH104" s="8">
+        <f t="shared" si="28"/>
+        <v>0.94100000000000006</v>
+      </c>
       <c r="AI104" s="8"/>
       <c r="AJ104" s="8"/>
       <c r="AK104" s="8"/>
@@ -17609,7 +17900,7 @@
         <v>64</v>
       </c>
       <c r="L105" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-7</v>
       </c>
       <c r="M105" s="8"/>
@@ -17618,7 +17909,7 @@
         <v>9</v>
       </c>
       <c r="P105" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>11.4</v>
       </c>
       <c r="Q105" s="4">
@@ -17626,16 +17917,16 @@
         <v>93.600000000000009</v>
       </c>
       <c r="R105" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>94</v>
       </c>
-      <c r="S105" s="19"/>
+      <c r="S105" s="8"/>
       <c r="T105" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>9.0350877192982448</v>
       </c>
       <c r="U105" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0.78947368421052633</v>
       </c>
       <c r="V105" s="8">
@@ -17670,10 +17961,13 @@
       </c>
       <c r="AF105" s="8"/>
       <c r="AG105" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>37.6</v>
       </c>
-      <c r="AH105" s="8"/>
+      <c r="AH105" s="8">
+        <f t="shared" si="28"/>
+        <v>4.5600000000000005</v>
+      </c>
       <c r="AI105" s="8"/>
       <c r="AJ105" s="8"/>
       <c r="AK105" s="8"/>
@@ -17724,7 +18018,7 @@
         <v>69</v>
       </c>
       <c r="L106" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="M106" s="8"/>
@@ -17733,7 +18027,7 @@
         <v>0</v>
       </c>
       <c r="P106" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>13.8</v>
       </c>
       <c r="Q106" s="4">
@@ -17741,16 +18035,16 @@
         <v>114.60000000000002</v>
       </c>
       <c r="R106" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>115</v>
       </c>
-      <c r="S106" s="19"/>
+      <c r="S106" s="8"/>
       <c r="T106" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>12.028985507246377</v>
       </c>
       <c r="U106" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>3.6956521739130435</v>
       </c>
       <c r="V106" s="8">
@@ -17785,10 +18079,13 @@
       </c>
       <c r="AF106" s="8"/>
       <c r="AG106" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>40.25</v>
       </c>
-      <c r="AH106" s="8"/>
+      <c r="AH106" s="8">
+        <f t="shared" si="28"/>
+        <v>4.83</v>
+      </c>
       <c r="AI106" s="8"/>
       <c r="AJ106" s="8"/>
       <c r="AK106" s="8"/>
@@ -17837,7 +18134,7 @@
         <v>2</v>
       </c>
       <c r="L107" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.42899999999999983</v>
       </c>
       <c r="M107" s="8"/>
@@ -17846,21 +18143,21 @@
         <v>0</v>
       </c>
       <c r="P107" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.48579999999999995</v>
       </c>
       <c r="Q107" s="4"/>
       <c r="R107" s="4">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S107" s="19"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S107" s="8"/>
       <c r="T107" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>164.47097571016883</v>
       </c>
       <c r="U107" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>164.47097571016883</v>
       </c>
       <c r="V107" s="8">
@@ -17897,10 +18194,13 @@
         <v>148</v>
       </c>
       <c r="AG107" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH107" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH107" s="8">
+        <f t="shared" si="28"/>
+        <v>0.48579999999999995</v>
+      </c>
       <c r="AI107" s="8"/>
       <c r="AJ107" s="8"/>
       <c r="AK107" s="8"/>
@@ -17949,7 +18249,7 @@
         <v>17.100000000000001</v>
       </c>
       <c r="L108" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-3.5000000000000018</v>
       </c>
       <c r="M108" s="8"/>
@@ -17958,7 +18258,7 @@
         <v>0</v>
       </c>
       <c r="P108" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2.7199999999999998</v>
       </c>
       <c r="Q108" s="4">
@@ -17966,16 +18266,16 @@
         <v>20.739000000000001</v>
       </c>
       <c r="R108" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>21</v>
       </c>
-      <c r="S108" s="19"/>
+      <c r="S108" s="8"/>
       <c r="T108" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>12.095955882352941</v>
       </c>
       <c r="U108" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>4.3753676470588241</v>
       </c>
       <c r="V108" s="8">
@@ -18010,10 +18310,13 @@
       </c>
       <c r="AF108" s="8"/>
       <c r="AG108" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>21</v>
       </c>
-      <c r="AH108" s="8"/>
+      <c r="AH108" s="8">
+        <f t="shared" si="28"/>
+        <v>2.7199999999999998</v>
+      </c>
       <c r="AI108" s="8"/>
       <c r="AJ108" s="8"/>
       <c r="AK108" s="8"/>
@@ -18064,7 +18367,7 @@
         <v>70</v>
       </c>
       <c r="L109" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-2</v>
       </c>
       <c r="M109" s="8"/>
@@ -18073,21 +18376,21 @@
         <v>0</v>
       </c>
       <c r="P109" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>13.6</v>
       </c>
       <c r="Q109" s="4"/>
       <c r="R109" s="4">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S109" s="19"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S109" s="8"/>
       <c r="T109" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>20.22058823529412</v>
       </c>
       <c r="U109" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>20.22058823529412</v>
       </c>
       <c r="V109" s="8">
@@ -18120,14 +18423,17 @@
       <c r="AE109" s="8">
         <v>11</v>
       </c>
-      <c r="AF109" s="10" t="s">
+      <c r="AF109" s="9" t="s">
         <v>73</v>
       </c>
       <c r="AG109" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH109" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH109" s="8">
+        <f t="shared" si="28"/>
+        <v>4.4880000000000004</v>
+      </c>
       <c r="AI109" s="8"/>
       <c r="AJ109" s="8"/>
       <c r="AK109" s="8"/>
@@ -18146,98 +18452,101 @@
       <c r="AX109" s="8"/>
     </row>
     <row r="110" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A110" s="11" t="s">
+      <c r="A110" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B110" s="11" t="s">
+      <c r="B110" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C110" s="11">
+      <c r="C110" s="10">
         <v>16</v>
       </c>
-      <c r="D110" s="11">
+      <c r="D110" s="10">
         <v>35</v>
       </c>
-      <c r="E110" s="11">
+      <c r="E110" s="10">
         <v>15</v>
       </c>
-      <c r="F110" s="11"/>
-      <c r="G110" s="12">
-        <v>0</v>
-      </c>
-      <c r="H110" s="11">
+      <c r="F110" s="10"/>
+      <c r="G110" s="11">
+        <v>0</v>
+      </c>
+      <c r="H110" s="10">
         <v>45</v>
       </c>
-      <c r="I110" s="11" t="s">
+      <c r="I110" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="J110" s="11"/>
-      <c r="K110" s="11">
+      <c r="J110" s="10"/>
+      <c r="K110" s="10">
         <v>28</v>
       </c>
-      <c r="L110" s="11">
-        <f t="shared" si="35"/>
+      <c r="L110" s="10">
+        <f t="shared" si="37"/>
         <v>-13</v>
       </c>
-      <c r="M110" s="11"/>
-      <c r="N110" s="11"/>
-      <c r="O110" s="11">
-        <v>0</v>
-      </c>
-      <c r="P110" s="11">
-        <f t="shared" si="36"/>
+      <c r="M110" s="10"/>
+      <c r="N110" s="10"/>
+      <c r="O110" s="10">
+        <v>0</v>
+      </c>
+      <c r="P110" s="10">
+        <f t="shared" si="38"/>
         <v>3</v>
       </c>
-      <c r="Q110" s="13"/>
+      <c r="Q110" s="12"/>
       <c r="R110" s="4">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S110" s="19"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S110" s="8"/>
       <c r="T110" s="8">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="U110" s="11">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="V110" s="11">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="U110" s="10">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="V110" s="10">
         <v>6.4</v>
       </c>
-      <c r="W110" s="11">
+      <c r="W110" s="10">
         <v>0.4</v>
       </c>
-      <c r="X110" s="11">
+      <c r="X110" s="10">
         <v>1.8</v>
       </c>
-      <c r="Y110" s="11">
+      <c r="Y110" s="10">
         <v>6.6</v>
       </c>
-      <c r="Z110" s="11">
+      <c r="Z110" s="10">
         <v>3.4</v>
       </c>
-      <c r="AA110" s="11">
+      <c r="AA110" s="10">
         <v>3.4</v>
       </c>
-      <c r="AB110" s="11">
+      <c r="AB110" s="10">
         <v>4</v>
       </c>
-      <c r="AC110" s="11">
+      <c r="AC110" s="10">
         <v>2.8</v>
       </c>
-      <c r="AD110" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE110" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF110" s="11"/>
+      <c r="AD110" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE110" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF110" s="10"/>
       <c r="AG110" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH110" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH110" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AI110" s="8"/>
       <c r="AJ110" s="8"/>
       <c r="AK110" s="8"/>
@@ -18256,98 +18565,101 @@
       <c r="AX110" s="8"/>
     </row>
     <row r="111" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A111" s="11" t="s">
+      <c r="A111" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B111" s="11" t="s">
+      <c r="B111" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C111" s="11">
+      <c r="C111" s="10">
         <v>18</v>
       </c>
-      <c r="D111" s="11">
+      <c r="D111" s="10">
         <v>15</v>
       </c>
-      <c r="E111" s="11">
+      <c r="E111" s="10">
         <v>3</v>
       </c>
-      <c r="F111" s="11"/>
-      <c r="G111" s="12">
-        <v>0</v>
-      </c>
-      <c r="H111" s="11">
+      <c r="F111" s="10"/>
+      <c r="G111" s="11">
+        <v>0</v>
+      </c>
+      <c r="H111" s="10">
         <v>60</v>
       </c>
-      <c r="I111" s="11" t="s">
+      <c r="I111" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="J111" s="11"/>
-      <c r="K111" s="11">
+      <c r="J111" s="10"/>
+      <c r="K111" s="10">
         <v>41</v>
       </c>
-      <c r="L111" s="11">
-        <f t="shared" si="35"/>
+      <c r="L111" s="10">
+        <f t="shared" si="37"/>
         <v>-38</v>
       </c>
-      <c r="M111" s="11"/>
-      <c r="N111" s="11"/>
-      <c r="O111" s="11">
-        <v>0</v>
-      </c>
-      <c r="P111" s="11">
-        <f t="shared" si="36"/>
+      <c r="M111" s="10"/>
+      <c r="N111" s="10"/>
+      <c r="O111" s="10">
+        <v>0</v>
+      </c>
+      <c r="P111" s="10">
+        <f t="shared" si="38"/>
         <v>0.6</v>
       </c>
-      <c r="Q111" s="13"/>
+      <c r="Q111" s="12"/>
       <c r="R111" s="4">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S111" s="19"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S111" s="8"/>
       <c r="T111" s="8">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="U111" s="11">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="V111" s="11">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="U111" s="10">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="V111" s="10">
         <v>5.4</v>
       </c>
-      <c r="W111" s="11">
+      <c r="W111" s="10">
         <v>5.2</v>
       </c>
-      <c r="X111" s="11">
+      <c r="X111" s="10">
         <v>0.6</v>
       </c>
-      <c r="Y111" s="11">
+      <c r="Y111" s="10">
         <v>7.4</v>
       </c>
-      <c r="Z111" s="11">
+      <c r="Z111" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AA111" s="11">
+      <c r="AA111" s="10">
         <v>5</v>
       </c>
-      <c r="AB111" s="11">
+      <c r="AB111" s="10">
         <v>5.6</v>
       </c>
-      <c r="AC111" s="11">
+      <c r="AC111" s="10">
         <v>7.2</v>
       </c>
-      <c r="AD111" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE111" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF111" s="11"/>
+      <c r="AD111" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="10"/>
       <c r="AG111" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH111" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH111" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AI111" s="8"/>
       <c r="AJ111" s="8"/>
       <c r="AK111" s="8"/>
@@ -18398,7 +18710,7 @@
         <v>141</v>
       </c>
       <c r="L112" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-2</v>
       </c>
       <c r="M112" s="8"/>
@@ -18407,24 +18719,24 @@
         <v>0</v>
       </c>
       <c r="P112" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>27.8</v>
       </c>
       <c r="Q112" s="4">
-        <f t="shared" ref="Q112:Q114" si="38">15*P112-O112-F112</f>
+        <f t="shared" ref="Q112:Q114" si="40">15*P112-O112-F112</f>
         <v>168</v>
       </c>
       <c r="R112" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>168</v>
       </c>
-      <c r="S112" s="19"/>
+      <c r="S112" s="8"/>
       <c r="T112" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>15</v>
       </c>
       <c r="U112" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>8.956834532374101</v>
       </c>
       <c r="V112" s="8">
@@ -18459,10 +18771,13 @@
       </c>
       <c r="AF112" s="8"/>
       <c r="AG112" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>16.8</v>
       </c>
-      <c r="AH112" s="8"/>
+      <c r="AH112" s="8">
+        <f t="shared" si="28"/>
+        <v>2.7800000000000002</v>
+      </c>
       <c r="AI112" s="8"/>
       <c r="AJ112" s="8"/>
       <c r="AK112" s="8"/>
@@ -18511,7 +18826,7 @@
         <v>146</v>
       </c>
       <c r="L113" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-122</v>
       </c>
       <c r="M113" s="8"/>
@@ -18520,23 +18835,23 @@
         <v>88</v>
       </c>
       <c r="P113" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>4.8</v>
       </c>
       <c r="Q113" s="4">
         <v>100</v>
       </c>
       <c r="R113" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
-      <c r="S113" s="19"/>
+      <c r="S113" s="8"/>
       <c r="T113" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>39.166666666666671</v>
       </c>
       <c r="U113" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>18.333333333333336</v>
       </c>
       <c r="V113" s="8">
@@ -18569,14 +18884,17 @@
       <c r="AE113" s="8">
         <v>0</v>
       </c>
-      <c r="AF113" s="17" t="s">
+      <c r="AF113" s="16" t="s">
         <v>173</v>
       </c>
       <c r="AG113" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10</v>
       </c>
-      <c r="AH113" s="8"/>
+      <c r="AH113" s="8">
+        <f t="shared" si="28"/>
+        <v>0.48</v>
+      </c>
       <c r="AI113" s="8"/>
       <c r="AJ113" s="8"/>
       <c r="AK113" s="8"/>
@@ -18627,7 +18945,7 @@
         <v>58</v>
       </c>
       <c r="L114" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-2</v>
       </c>
       <c r="M114" s="8"/>
@@ -18636,24 +18954,24 @@
         <v>34</v>
       </c>
       <c r="P114" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>11.2</v>
       </c>
       <c r="Q114" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>14</v>
       </c>
       <c r="R114" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>14</v>
       </c>
-      <c r="S114" s="19"/>
+      <c r="S114" s="8"/>
       <c r="T114" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>15.000000000000002</v>
       </c>
       <c r="U114" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>13.75</v>
       </c>
       <c r="V114" s="8">
@@ -18690,10 +19008,13 @@
         <v>162</v>
       </c>
       <c r="AG114" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>5.6000000000000005</v>
       </c>
-      <c r="AH114" s="8"/>
+      <c r="AH114" s="8">
+        <f t="shared" si="28"/>
+        <v>4.4799999999999995</v>
+      </c>
       <c r="AI114" s="8"/>
       <c r="AJ114" s="8"/>
       <c r="AK114" s="8"/>
@@ -18740,7 +19061,7 @@
         <v>10</v>
       </c>
       <c r="L115" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-1</v>
       </c>
       <c r="M115" s="8"/>
@@ -18749,7 +19070,7 @@
         <v>0</v>
       </c>
       <c r="P115" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>1.8</v>
       </c>
       <c r="Q115" s="4">
@@ -18757,16 +19078,16 @@
         <v>15.2</v>
       </c>
       <c r="R115" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>15</v>
       </c>
-      <c r="S115" s="19"/>
+      <c r="S115" s="8"/>
       <c r="T115" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>8.8888888888888893</v>
       </c>
       <c r="U115" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="V115" s="8">
@@ -18803,10 +19124,13 @@
         <v>164</v>
       </c>
       <c r="AG115" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1.5</v>
       </c>
-      <c r="AH115" s="8"/>
+      <c r="AH115" s="8">
+        <f t="shared" si="28"/>
+        <v>0.18000000000000002</v>
+      </c>
       <c r="AI115" s="8"/>
       <c r="AJ115" s="8"/>
       <c r="AK115" s="8"/>
@@ -18853,7 +19177,7 @@
         <v>3</v>
       </c>
       <c r="L116" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="M116" s="8"/>
@@ -18862,21 +19186,21 @@
         <v>8</v>
       </c>
       <c r="P116" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.6</v>
       </c>
       <c r="Q116" s="4"/>
       <c r="R116" s="4">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S116" s="19"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S116" s="8"/>
       <c r="T116" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>13.333333333333334</v>
       </c>
       <c r="U116" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>13.333333333333334</v>
       </c>
       <c r="V116" s="8">
@@ -18913,10 +19237,13 @@
         <v>166</v>
       </c>
       <c r="AG116" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH116" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH116" s="8">
+        <f t="shared" si="28"/>
+        <v>0.06</v>
+      </c>
       <c r="AI116" s="8"/>
       <c r="AJ116" s="8"/>
       <c r="AK116" s="8"/>
@@ -18965,7 +19292,7 @@
         <v>18</v>
       </c>
       <c r="L117" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="M117" s="8"/>
@@ -18974,21 +19301,21 @@
         <v>0</v>
       </c>
       <c r="P117" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>3.6</v>
       </c>
       <c r="Q117" s="4"/>
       <c r="R117" s="4">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S117" s="19"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S117" s="8"/>
       <c r="T117" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>21.111111111111111</v>
       </c>
       <c r="U117" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>21.111111111111111</v>
       </c>
       <c r="V117" s="8">
@@ -19025,10 +19352,13 @@
         <v>37</v>
       </c>
       <c r="AG117" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH117" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH117" s="8">
+        <f t="shared" si="28"/>
+        <v>1.08</v>
+      </c>
       <c r="AI117" s="8"/>
       <c r="AJ117" s="8"/>
       <c r="AK117" s="8"/>
@@ -19047,90 +19377,93 @@
       <c r="AX117" s="8"/>
     </row>
     <row r="118" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A118" s="11" t="s">
+      <c r="A118" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B118" s="11" t="s">
+      <c r="B118" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C118" s="11"/>
-      <c r="D118" s="11"/>
-      <c r="E118" s="11"/>
-      <c r="F118" s="11"/>
-      <c r="G118" s="12">
-        <v>0</v>
-      </c>
-      <c r="H118" s="11"/>
-      <c r="I118" s="11" t="s">
+      <c r="C118" s="10"/>
+      <c r="D118" s="10"/>
+      <c r="E118" s="10"/>
+      <c r="F118" s="10"/>
+      <c r="G118" s="11">
+        <v>0</v>
+      </c>
+      <c r="H118" s="10"/>
+      <c r="I118" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J118" s="11"/>
-      <c r="K118" s="11"/>
-      <c r="L118" s="11">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="M118" s="11"/>
-      <c r="N118" s="11"/>
-      <c r="O118" s="11">
-        <v>0</v>
-      </c>
-      <c r="P118" s="11">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="Q118" s="13"/>
+      <c r="J118" s="10"/>
+      <c r="K118" s="10"/>
+      <c r="L118" s="10">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M118" s="10"/>
+      <c r="N118" s="10"/>
+      <c r="O118" s="10">
+        <v>0</v>
+      </c>
+      <c r="P118" s="10">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="Q118" s="12"/>
       <c r="R118" s="4">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S118" s="19"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S118" s="8"/>
       <c r="T118" s="8" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U118" s="11" t="e">
-        <f t="shared" si="37"/>
+      <c r="U118" s="10" t="e">
+        <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V118" s="11">
-        <v>0</v>
-      </c>
-      <c r="W118" s="11">
-        <v>0</v>
-      </c>
-      <c r="X118" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y118" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z118" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA118" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB118" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC118" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD118" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE118" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF118" s="11" t="s">
+      <c r="V118" s="10">
+        <v>0</v>
+      </c>
+      <c r="W118" s="10">
+        <v>0</v>
+      </c>
+      <c r="X118" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y118" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z118" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA118" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB118" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC118" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD118" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE118" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF118" s="10" t="s">
         <v>86</v>
       </c>
       <c r="AG118" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH118" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH118" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AI118" s="8"/>
       <c r="AJ118" s="8"/>
       <c r="AK118" s="8"/>
@@ -19149,96 +19482,99 @@
       <c r="AX118" s="8"/>
     </row>
     <row r="119" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A119" s="11" t="s">
+      <c r="A119" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="B119" s="11" t="s">
+      <c r="B119" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C119" s="11">
+      <c r="C119" s="10">
         <v>22</v>
       </c>
-      <c r="D119" s="11">
+      <c r="D119" s="10">
         <v>7</v>
       </c>
-      <c r="E119" s="11"/>
-      <c r="F119" s="15">
+      <c r="E119" s="10"/>
+      <c r="F119" s="14">
         <v>29</v>
       </c>
-      <c r="G119" s="12">
-        <v>0</v>
-      </c>
-      <c r="H119" s="11"/>
-      <c r="I119" s="11" t="s">
+      <c r="G119" s="11">
+        <v>0</v>
+      </c>
+      <c r="H119" s="10"/>
+      <c r="I119" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="J119" s="11" t="s">
+      <c r="J119" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="K119" s="11"/>
-      <c r="L119" s="11">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="M119" s="11"/>
-      <c r="N119" s="11"/>
-      <c r="O119" s="11">
-        <v>0</v>
-      </c>
-      <c r="P119" s="11">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="Q119" s="13"/>
+      <c r="K119" s="10"/>
+      <c r="L119" s="10">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M119" s="10"/>
+      <c r="N119" s="10"/>
+      <c r="O119" s="10">
+        <v>0</v>
+      </c>
+      <c r="P119" s="10">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="Q119" s="12"/>
       <c r="R119" s="4">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S119" s="19"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="S119" s="8"/>
       <c r="T119" s="8" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U119" s="11" t="e">
-        <f t="shared" si="37"/>
+      <c r="U119" s="10" t="e">
+        <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V119" s="11">
-        <v>0</v>
-      </c>
-      <c r="W119" s="11">
-        <v>0</v>
-      </c>
-      <c r="X119" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y119" s="11">
+      <c r="V119" s="10">
+        <v>0</v>
+      </c>
+      <c r="W119" s="10">
+        <v>0</v>
+      </c>
+      <c r="X119" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y119" s="10">
         <v>1.4</v>
       </c>
-      <c r="Z119" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA119" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB119" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC119" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD119" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE119" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF119" s="11"/>
+      <c r="Z119" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA119" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB119" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC119" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD119" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE119" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF119" s="10"/>
       <c r="AG119" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AH119" s="8"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH119" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AI119" s="8"/>
       <c r="AJ119" s="8"/>
       <c r="AK119" s="8"/>
